--- a/packages/GB Accounts Self Employed 2022-04-05 (Apr22) Excel 2007/Vat.xlsx
+++ b/packages/GB Accounts Self Employed 2022-04-05 (Apr22) Excel 2007/Vat.xlsx
@@ -1347,87 +1347,87 @@
       <sheetData sheetId="9">
         <row r="2">
           <cell r="B2">
-            <v>45716</v>
+            <v>44255</v>
           </cell>
         </row>
         <row r="3">
           <cell r="B3">
-            <v>45747</v>
+            <v>44286</v>
           </cell>
         </row>
         <row r="5">
           <cell r="B5">
-            <v>45777</v>
+            <v>44316</v>
           </cell>
         </row>
         <row r="6">
           <cell r="B6">
-            <v>45808</v>
+            <v>44347</v>
           </cell>
         </row>
         <row r="7">
           <cell r="B7">
-            <v>45838</v>
+            <v>44377</v>
           </cell>
         </row>
         <row r="8">
           <cell r="B8">
-            <v>45869</v>
+            <v>44408</v>
           </cell>
         </row>
         <row r="9">
           <cell r="B9">
-            <v>45900</v>
+            <v>44439</v>
           </cell>
         </row>
         <row r="10">
           <cell r="B10">
-            <v>45930</v>
+            <v>44469</v>
           </cell>
         </row>
         <row r="11">
           <cell r="B11">
-            <v>45961</v>
+            <v>44500</v>
           </cell>
         </row>
         <row r="12">
           <cell r="B12">
-            <v>45991</v>
+            <v>44530</v>
           </cell>
         </row>
         <row r="13">
           <cell r="B13">
-            <v>46022</v>
+            <v>44561</v>
           </cell>
         </row>
         <row r="14">
           <cell r="B14">
-            <v>46053</v>
+            <v>44592</v>
           </cell>
         </row>
         <row r="15">
           <cell r="B15">
-            <v>46081</v>
+            <v>44620</v>
           </cell>
         </row>
         <row r="16">
           <cell r="B16">
-            <v>46112</v>
+            <v>44651</v>
           </cell>
         </row>
         <row r="18">
           <cell r="B18">
-            <v>46142</v>
+            <v>44681</v>
           </cell>
         </row>
         <row r="19">
           <cell r="B19">
-            <v>46173</v>
+            <v>44712</v>
           </cell>
         </row>
         <row r="20">
           <cell r="B20">
-            <v>46203</v>
+            <v>44742</v>
           </cell>
         </row>
       </sheetData>
@@ -2150,7 +2150,7 @@
       <c r="I2" s="13"/>
       <c r="K2" s="69">
         <f>[1]Admin!$B$5</f>
-        <v>45777</v>
+        <v>44316</v>
       </c>
     </row>
     <row r="3" spans="1:11" ht="14" thickBot="1" x14ac:dyDescent="0.2">
@@ -2167,7 +2167,7 @@
       <c r="I3" s="13"/>
       <c r="K3" s="69">
         <f>[1]Admin!$B$6</f>
-        <v>45808</v>
+        <v>44347</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="16.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.2">
@@ -2184,7 +2184,7 @@
       <c r="I4" s="13"/>
       <c r="K4" s="69">
         <f>[1]Admin!$B$7</f>
-        <v>45838</v>
+        <v>44377</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.15">
@@ -2203,7 +2203,7 @@
       <c r="I5" s="13"/>
       <c r="K5" s="69">
         <f>[1]Admin!$B$8</f>
-        <v>45869</v>
+        <v>44408</v>
       </c>
     </row>
     <row r="6" spans="1:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
@@ -2218,7 +2218,7 @@
       <c r="I6" s="13"/>
       <c r="K6" s="69">
         <f>[1]Admin!$B$9</f>
-        <v>45900</v>
+        <v>44439</v>
       </c>
     </row>
     <row r="7" spans="1:11" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
@@ -2238,7 +2238,7 @@
       <c r="I7" s="13"/>
       <c r="K7" s="69">
         <f>[1]Admin!$B$10</f>
-        <v>45930</v>
+        <v>44469</v>
       </c>
     </row>
     <row r="8" spans="1:11" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.2">
@@ -2253,7 +2253,7 @@
       <c r="I8" s="13"/>
       <c r="K8" s="69">
         <f>[1]Admin!$B$11</f>
-        <v>45961</v>
+        <v>44500</v>
       </c>
     </row>
     <row r="9" spans="1:11" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
@@ -2275,7 +2275,7 @@
       <c r="I9" s="13"/>
       <c r="K9" s="69">
         <f>[1]Admin!$B$12</f>
-        <v>45991</v>
+        <v>44530</v>
       </c>
     </row>
     <row r="10" spans="1:11" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
@@ -2290,7 +2290,7 @@
       <c r="I10" s="13"/>
       <c r="K10" s="69">
         <f>[1]Admin!$B$13</f>
-        <v>46022</v>
+        <v>44561</v>
       </c>
     </row>
     <row r="11" spans="1:11" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
@@ -2311,7 +2311,7 @@
       <c r="I11" s="13"/>
       <c r="K11" s="69">
         <f>[1]Admin!$B$14</f>
-        <v>46053</v>
+        <v>44592</v>
       </c>
     </row>
     <row r="12" spans="1:11" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
@@ -2326,7 +2326,7 @@
       <c r="I12" s="13"/>
       <c r="K12" s="69">
         <f>[1]Admin!$B$15</f>
-        <v>46081</v>
+        <v>44620</v>
       </c>
     </row>
     <row r="13" spans="1:11" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
@@ -2348,7 +2348,7 @@
       <c r="I13" s="13"/>
       <c r="K13" s="69">
         <f>[1]Admin!$B$16</f>
-        <v>46112</v>
+        <v>44651</v>
       </c>
     </row>
     <row r="14" spans="1:11" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
@@ -2363,7 +2363,7 @@
       <c r="I14" s="13"/>
       <c r="K14" s="69">
         <f>[1]Admin!$B$18</f>
-        <v>46142</v>
+        <v>44681</v>
       </c>
     </row>
     <row r="15" spans="1:11" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
@@ -2385,7 +2385,7 @@
       <c r="I15" s="13"/>
       <c r="K15" s="69">
         <f>[1]Admin!$B$19</f>
-        <v>46173</v>
+        <v>44712</v>
       </c>
     </row>
     <row r="16" spans="1:11" ht="14" thickBot="1" x14ac:dyDescent="0.2">
@@ -13921,7 +13921,7 @@
       <c r="I2" s="13"/>
       <c r="K2" s="69">
         <f>[1]Admin!$B$5</f>
-        <v>45777</v>
+        <v>44316</v>
       </c>
     </row>
     <row r="3" spans="1:11" ht="14" thickBot="1" x14ac:dyDescent="0.2">
@@ -13938,7 +13938,7 @@
       <c r="I3" s="13"/>
       <c r="K3" s="69">
         <f>[1]Admin!$B$6</f>
-        <v>45808</v>
+        <v>44347</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="16.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.2">
@@ -13955,7 +13955,7 @@
       <c r="I4" s="13"/>
       <c r="K4" s="69">
         <f>[1]Admin!$B$7</f>
-        <v>45838</v>
+        <v>44377</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.15">
@@ -13974,7 +13974,7 @@
       <c r="I5" s="13"/>
       <c r="K5" s="69">
         <f>[1]Admin!$B$8</f>
-        <v>45869</v>
+        <v>44408</v>
       </c>
     </row>
     <row r="6" spans="1:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
@@ -13989,7 +13989,7 @@
       <c r="I6" s="13"/>
       <c r="K6" s="69">
         <f>[1]Admin!$B$9</f>
-        <v>45900</v>
+        <v>44439</v>
       </c>
     </row>
     <row r="7" spans="1:11" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
@@ -14009,7 +14009,7 @@
       <c r="I7" s="13"/>
       <c r="K7" s="69">
         <f>[1]Admin!$B$10</f>
-        <v>45930</v>
+        <v>44469</v>
       </c>
     </row>
     <row r="8" spans="1:11" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.2">
@@ -14024,7 +14024,7 @@
       <c r="I8" s="13"/>
       <c r="K8" s="69">
         <f>[1]Admin!$B$11</f>
-        <v>45961</v>
+        <v>44500</v>
       </c>
     </row>
     <row r="9" spans="1:11" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
@@ -14046,7 +14046,7 @@
       <c r="I9" s="13"/>
       <c r="K9" s="69">
         <f>[1]Admin!$B$12</f>
-        <v>45991</v>
+        <v>44530</v>
       </c>
     </row>
     <row r="10" spans="1:11" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
@@ -14061,7 +14061,7 @@
       <c r="I10" s="13"/>
       <c r="K10" s="69">
         <f>[1]Admin!$B$13</f>
-        <v>46022</v>
+        <v>44561</v>
       </c>
     </row>
     <row r="11" spans="1:11" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
@@ -14082,7 +14082,7 @@
       <c r="I11" s="13"/>
       <c r="K11" s="69">
         <f>[1]Admin!$B$14</f>
-        <v>46053</v>
+        <v>44592</v>
       </c>
     </row>
     <row r="12" spans="1:11" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
@@ -14097,7 +14097,7 @@
       <c r="I12" s="13"/>
       <c r="K12" s="69">
         <f>[1]Admin!$B$15</f>
-        <v>46081</v>
+        <v>44620</v>
       </c>
     </row>
     <row r="13" spans="1:11" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
@@ -14119,7 +14119,7 @@
       <c r="I13" s="13"/>
       <c r="K13" s="69">
         <f>[1]Admin!$B$16</f>
-        <v>46112</v>
+        <v>44651</v>
       </c>
     </row>
     <row r="14" spans="1:11" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
@@ -14134,7 +14134,7 @@
       <c r="I14" s="13"/>
       <c r="K14" s="69">
         <f>[1]Admin!$B$18</f>
-        <v>46142</v>
+        <v>44681</v>
       </c>
     </row>
     <row r="15" spans="1:11" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
@@ -14156,7 +14156,7 @@
       <c r="I15" s="13"/>
       <c r="K15" s="69">
         <f>[1]Admin!$B$19</f>
-        <v>46173</v>
+        <v>44712</v>
       </c>
     </row>
     <row r="16" spans="1:11" ht="14" thickBot="1" x14ac:dyDescent="0.2">
@@ -14467,7 +14467,7 @@
       <c r="I2" s="13"/>
       <c r="K2" s="69">
         <f>[1]Admin!$B$5</f>
-        <v>45777</v>
+        <v>44316</v>
       </c>
     </row>
     <row r="3" spans="1:11" ht="14" thickBot="1" x14ac:dyDescent="0.2">
@@ -14484,7 +14484,7 @@
       <c r="I3" s="13"/>
       <c r="K3" s="69">
         <f>[1]Admin!$B$6</f>
-        <v>45808</v>
+        <v>44347</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="16.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.2">
@@ -14501,7 +14501,7 @@
       <c r="I4" s="13"/>
       <c r="K4" s="69">
         <f>[1]Admin!$B$7</f>
-        <v>45838</v>
+        <v>44377</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.15">
@@ -14520,7 +14520,7 @@
       <c r="I5" s="13"/>
       <c r="K5" s="69">
         <f>[1]Admin!$B$8</f>
-        <v>45869</v>
+        <v>44408</v>
       </c>
     </row>
     <row r="6" spans="1:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
@@ -14535,7 +14535,7 @@
       <c r="I6" s="13"/>
       <c r="K6" s="69">
         <f>[1]Admin!$B$9</f>
-        <v>45900</v>
+        <v>44439</v>
       </c>
     </row>
     <row r="7" spans="1:11" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
@@ -14555,7 +14555,7 @@
       <c r="I7" s="13"/>
       <c r="K7" s="69">
         <f>[1]Admin!$B$10</f>
-        <v>45930</v>
+        <v>44469</v>
       </c>
     </row>
     <row r="8" spans="1:11" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.2">
@@ -14570,7 +14570,7 @@
       <c r="I8" s="13"/>
       <c r="K8" s="69">
         <f>[1]Admin!$B$11</f>
-        <v>45961</v>
+        <v>44500</v>
       </c>
     </row>
     <row r="9" spans="1:11" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
@@ -14592,7 +14592,7 @@
       <c r="I9" s="13"/>
       <c r="K9" s="69">
         <f>[1]Admin!$B$12</f>
-        <v>45991</v>
+        <v>44530</v>
       </c>
     </row>
     <row r="10" spans="1:11" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
@@ -14607,7 +14607,7 @@
       <c r="I10" s="13"/>
       <c r="K10" s="69">
         <f>[1]Admin!$B$13</f>
-        <v>46022</v>
+        <v>44561</v>
       </c>
     </row>
     <row r="11" spans="1:11" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
@@ -14628,7 +14628,7 @@
       <c r="I11" s="13"/>
       <c r="K11" s="69">
         <f>[1]Admin!$B$14</f>
-        <v>46053</v>
+        <v>44592</v>
       </c>
     </row>
     <row r="12" spans="1:11" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
@@ -14643,7 +14643,7 @@
       <c r="I12" s="13"/>
       <c r="K12" s="69">
         <f>[1]Admin!$B$15</f>
-        <v>46081</v>
+        <v>44620</v>
       </c>
     </row>
     <row r="13" spans="1:11" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
@@ -14665,7 +14665,7 @@
       <c r="I13" s="13"/>
       <c r="K13" s="69">
         <f>[1]Admin!$B$16</f>
-        <v>46112</v>
+        <v>44651</v>
       </c>
     </row>
     <row r="14" spans="1:11" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
@@ -14680,7 +14680,7 @@
       <c r="I14" s="13"/>
       <c r="K14" s="69">
         <f>[1]Admin!$B$18</f>
-        <v>46142</v>
+        <v>44681</v>
       </c>
     </row>
     <row r="15" spans="1:11" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
@@ -14702,7 +14702,7 @@
       <c r="I15" s="13"/>
       <c r="K15" s="69">
         <f>[1]Admin!$B$19</f>
-        <v>46173</v>
+        <v>44712</v>
       </c>
     </row>
     <row r="16" spans="1:11" ht="14" thickBot="1" x14ac:dyDescent="0.2">
@@ -15013,7 +15013,7 @@
       <c r="I2" s="13"/>
       <c r="K2" s="69">
         <f>[1]Admin!$B$5</f>
-        <v>45777</v>
+        <v>44316</v>
       </c>
     </row>
     <row r="3" spans="1:11" ht="14" thickBot="1" x14ac:dyDescent="0.2">
@@ -15030,7 +15030,7 @@
       <c r="I3" s="13"/>
       <c r="K3" s="69">
         <f>[1]Admin!$B$6</f>
-        <v>45808</v>
+        <v>44347</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="16.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.2">
@@ -15047,7 +15047,7 @@
       <c r="I4" s="13"/>
       <c r="K4" s="69">
         <f>[1]Admin!$B$7</f>
-        <v>45838</v>
+        <v>44377</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.15">
@@ -15066,7 +15066,7 @@
       <c r="I5" s="13"/>
       <c r="K5" s="69">
         <f>[1]Admin!$B$8</f>
-        <v>45869</v>
+        <v>44408</v>
       </c>
     </row>
     <row r="6" spans="1:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
@@ -15081,7 +15081,7 @@
       <c r="I6" s="13"/>
       <c r="K6" s="69">
         <f>[1]Admin!$B$9</f>
-        <v>45900</v>
+        <v>44439</v>
       </c>
     </row>
     <row r="7" spans="1:11" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
@@ -15101,7 +15101,7 @@
       <c r="I7" s="13"/>
       <c r="K7" s="69">
         <f>[1]Admin!$B$10</f>
-        <v>45930</v>
+        <v>44469</v>
       </c>
     </row>
     <row r="8" spans="1:11" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.2">
@@ -15116,7 +15116,7 @@
       <c r="I8" s="13"/>
       <c r="K8" s="69">
         <f>[1]Admin!$B$11</f>
-        <v>45961</v>
+        <v>44500</v>
       </c>
     </row>
     <row r="9" spans="1:11" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
@@ -15138,7 +15138,7 @@
       <c r="I9" s="13"/>
       <c r="K9" s="69">
         <f>[1]Admin!$B$12</f>
-        <v>45991</v>
+        <v>44530</v>
       </c>
     </row>
     <row r="10" spans="1:11" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
@@ -15153,7 +15153,7 @@
       <c r="I10" s="13"/>
       <c r="K10" s="69">
         <f>[1]Admin!$B$13</f>
-        <v>46022</v>
+        <v>44561</v>
       </c>
     </row>
     <row r="11" spans="1:11" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
@@ -15174,7 +15174,7 @@
       <c r="I11" s="13"/>
       <c r="K11" s="69">
         <f>[1]Admin!$B$14</f>
-        <v>46053</v>
+        <v>44592</v>
       </c>
     </row>
     <row r="12" spans="1:11" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
@@ -15189,7 +15189,7 @@
       <c r="I12" s="13"/>
       <c r="K12" s="69">
         <f>[1]Admin!$B$15</f>
-        <v>46081</v>
+        <v>44620</v>
       </c>
     </row>
     <row r="13" spans="1:11" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
@@ -15211,7 +15211,7 @@
       <c r="I13" s="13"/>
       <c r="K13" s="69">
         <f>[1]Admin!$B$16</f>
-        <v>46112</v>
+        <v>44651</v>
       </c>
     </row>
     <row r="14" spans="1:11" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
@@ -15226,7 +15226,7 @@
       <c r="I14" s="13"/>
       <c r="K14" s="69">
         <f>[1]Admin!$B$18</f>
-        <v>46142</v>
+        <v>44681</v>
       </c>
     </row>
     <row r="15" spans="1:11" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
@@ -15248,7 +15248,7 @@
       <c r="I15" s="13"/>
       <c r="K15" s="69">
         <f>[1]Admin!$B$19</f>
-        <v>46173</v>
+        <v>44712</v>
       </c>
     </row>
     <row r="16" spans="1:11" ht="14" thickBot="1" x14ac:dyDescent="0.2">
@@ -15559,7 +15559,7 @@
       <c r="I2" s="13"/>
       <c r="K2" s="69">
         <f>[1]Admin!$B$5</f>
-        <v>45777</v>
+        <v>44316</v>
       </c>
     </row>
     <row r="3" spans="1:11" ht="14" thickBot="1" x14ac:dyDescent="0.2">
@@ -15576,7 +15576,7 @@
       <c r="I3" s="13"/>
       <c r="K3" s="69">
         <f>[1]Admin!$B$6</f>
-        <v>45808</v>
+        <v>44347</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="16.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.2">
@@ -15593,7 +15593,7 @@
       <c r="I4" s="13"/>
       <c r="K4" s="69">
         <f>[1]Admin!$B$7</f>
-        <v>45838</v>
+        <v>44377</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.15">
@@ -15612,7 +15612,7 @@
       <c r="I5" s="13"/>
       <c r="K5" s="69">
         <f>[1]Admin!$B$8</f>
-        <v>45869</v>
+        <v>44408</v>
       </c>
     </row>
     <row r="6" spans="1:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
@@ -15627,7 +15627,7 @@
       <c r="I6" s="13"/>
       <c r="K6" s="69">
         <f>[1]Admin!$B$9</f>
-        <v>45900</v>
+        <v>44439</v>
       </c>
     </row>
     <row r="7" spans="1:11" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
@@ -15647,7 +15647,7 @@
       <c r="I7" s="13"/>
       <c r="K7" s="69">
         <f>[1]Admin!$B$10</f>
-        <v>45930</v>
+        <v>44469</v>
       </c>
     </row>
     <row r="8" spans="1:11" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.2">
@@ -15662,7 +15662,7 @@
       <c r="I8" s="13"/>
       <c r="K8" s="69">
         <f>[1]Admin!$B$11</f>
-        <v>45961</v>
+        <v>44500</v>
       </c>
     </row>
     <row r="9" spans="1:11" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
@@ -15684,7 +15684,7 @@
       <c r="I9" s="13"/>
       <c r="K9" s="69">
         <f>[1]Admin!$B$12</f>
-        <v>45991</v>
+        <v>44530</v>
       </c>
     </row>
     <row r="10" spans="1:11" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
@@ -15699,7 +15699,7 @@
       <c r="I10" s="13"/>
       <c r="K10" s="69">
         <f>[1]Admin!$B$13</f>
-        <v>46022</v>
+        <v>44561</v>
       </c>
     </row>
     <row r="11" spans="1:11" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
@@ -15720,7 +15720,7 @@
       <c r="I11" s="13"/>
       <c r="K11" s="69">
         <f>[1]Admin!$B$14</f>
-        <v>46053</v>
+        <v>44592</v>
       </c>
     </row>
     <row r="12" spans="1:11" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
@@ -15735,7 +15735,7 @@
       <c r="I12" s="13"/>
       <c r="K12" s="69">
         <f>[1]Admin!$B$15</f>
-        <v>46081</v>
+        <v>44620</v>
       </c>
     </row>
     <row r="13" spans="1:11" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
@@ -15757,7 +15757,7 @@
       <c r="I13" s="13"/>
       <c r="K13" s="69">
         <f>[1]Admin!$B$16</f>
-        <v>46112</v>
+        <v>44651</v>
       </c>
     </row>
     <row r="14" spans="1:11" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
@@ -15772,7 +15772,7 @@
       <c r="I14" s="13"/>
       <c r="K14" s="69">
         <f>[1]Admin!$B$18</f>
-        <v>46142</v>
+        <v>44681</v>
       </c>
     </row>
     <row r="15" spans="1:11" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
@@ -15794,7 +15794,7 @@
       <c r="I15" s="13"/>
       <c r="K15" s="69">
         <f>[1]Admin!$B$19</f>
-        <v>46173</v>
+        <v>44712</v>
       </c>
     </row>
     <row r="16" spans="1:11" ht="14" thickBot="1" x14ac:dyDescent="0.2">
@@ -16149,7 +16149,7 @@
       <c r="A4" s="56"/>
       <c r="B4" s="62">
         <f>[1]Admin!$B$2</f>
-        <v>45716</v>
+        <v>44255</v>
       </c>
       <c r="C4" s="62">
         <f>B5</f>
@@ -16186,7 +16186,7 @@
       <c r="A5" s="56"/>
       <c r="B5" s="62">
         <f>[1]Admin!$B$3</f>
-        <v>45747</v>
+        <v>44286</v>
       </c>
       <c r="C5" s="62">
         <f t="shared" ref="C5:C18" si="0">B6</f>
@@ -16223,7 +16223,7 @@
       <c r="A6" s="56"/>
       <c r="B6" s="62">
         <f>[1]Admin!$B$5</f>
-        <v>45777</v>
+        <v>44316</v>
       </c>
       <c r="C6" s="62">
         <f t="shared" si="0"/>
@@ -16272,7 +16272,7 @@
       <c r="A7" s="56"/>
       <c r="B7" s="62">
         <f>[1]Admin!$B$6</f>
-        <v>45808</v>
+        <v>44347</v>
       </c>
       <c r="C7" s="62">
         <f t="shared" si="0"/>
@@ -16321,7 +16321,7 @@
       <c r="A8" s="56"/>
       <c r="B8" s="62">
         <f>[1]Admin!$B$7</f>
-        <v>45838</v>
+        <v>44377</v>
       </c>
       <c r="C8" s="62">
         <f t="shared" si="0"/>
@@ -16370,7 +16370,7 @@
       <c r="A9" s="56"/>
       <c r="B9" s="62">
         <f>[1]Admin!$B$8</f>
-        <v>45869</v>
+        <v>44408</v>
       </c>
       <c r="C9" s="62">
         <f t="shared" si="0"/>
@@ -16419,7 +16419,7 @@
       <c r="A10" s="56"/>
       <c r="B10" s="62">
         <f>[1]Admin!$B$9</f>
-        <v>45900</v>
+        <v>44439</v>
       </c>
       <c r="C10" s="62">
         <f t="shared" si="0"/>
@@ -16468,7 +16468,7 @@
       <c r="A11" s="56"/>
       <c r="B11" s="62">
         <f>[1]Admin!$B$10</f>
-        <v>45930</v>
+        <v>44469</v>
       </c>
       <c r="C11" s="62">
         <f t="shared" si="0"/>
@@ -16517,7 +16517,7 @@
       <c r="A12" s="56"/>
       <c r="B12" s="62">
         <f>[1]Admin!$B$11</f>
-        <v>45961</v>
+        <v>44500</v>
       </c>
       <c r="C12" s="62">
         <f t="shared" si="0"/>
@@ -16566,7 +16566,7 @@
       <c r="A13" s="56"/>
       <c r="B13" s="62">
         <f>[1]Admin!$B$12</f>
-        <v>45991</v>
+        <v>44530</v>
       </c>
       <c r="C13" s="62">
         <f t="shared" si="0"/>
@@ -16615,7 +16615,7 @@
       <c r="A14" s="56"/>
       <c r="B14" s="62">
         <f>[1]Admin!$B$13</f>
-        <v>46022</v>
+        <v>44561</v>
       </c>
       <c r="C14" s="62">
         <f t="shared" si="0"/>
@@ -16664,7 +16664,7 @@
       <c r="A15" s="56"/>
       <c r="B15" s="62">
         <f>[1]Admin!$B$14</f>
-        <v>46053</v>
+        <v>44592</v>
       </c>
       <c r="C15" s="62">
         <f t="shared" si="0"/>
@@ -16713,7 +16713,7 @@
       <c r="A16" s="56"/>
       <c r="B16" s="62">
         <f>[1]Admin!$B$15</f>
-        <v>46081</v>
+        <v>44620</v>
       </c>
       <c r="C16" s="62">
         <f t="shared" si="0"/>
@@ -16762,7 +16762,7 @@
       <c r="A17" s="56"/>
       <c r="B17" s="62">
         <f>[1]Admin!$B$16</f>
-        <v>46112</v>
+        <v>44651</v>
       </c>
       <c r="C17" s="62">
         <f t="shared" si="0"/>
@@ -16811,7 +16811,7 @@
       <c r="A18" s="56"/>
       <c r="B18" s="62">
         <f>[1]Admin!$B$18</f>
-        <v>46142</v>
+        <v>44681</v>
       </c>
       <c r="C18" s="62">
         <f t="shared" si="0"/>
@@ -16860,11 +16860,11 @@
       <c r="A19" s="56"/>
       <c r="B19" s="62">
         <f>[1]Admin!$B$19</f>
-        <v>46173</v>
+        <v>44712</v>
       </c>
       <c r="C19" s="63">
         <f>[1]Admin!$B$20</f>
-        <v>46203</v>
+        <v>44742</v>
       </c>
       <c r="D19" s="107">
         <f>S05Y2!$G$1</f>

--- a/packages/GB Accounts Self Employed 2022-04-05 (Apr22) Excel 2007/Vat.xlsx
+++ b/packages/GB Accounts Self Employed 2022-04-05 (Apr22) Excel 2007/Vat.xlsx
@@ -2197,7 +2197,7 @@
       </c>
       <c r="F5" s="144"/>
       <c r="G5" s="42">
-        <v>44408</v>
+        <v>44377</v>
       </c>
       <c r="H5" s="10"/>
       <c r="I5" s="13"/>
@@ -13968,7 +13968,7 @@
       </c>
       <c r="F5" s="144"/>
       <c r="G5" s="42">
-        <v>44500</v>
+        <v>44469</v>
       </c>
       <c r="H5" s="10"/>
       <c r="I5" s="13"/>
@@ -14514,7 +14514,7 @@
       </c>
       <c r="F5" s="144"/>
       <c r="G5" s="42">
-        <v>44592</v>
+        <v>44561</v>
       </c>
       <c r="H5" s="10"/>
       <c r="I5" s="13"/>
@@ -15060,7 +15060,7 @@
       </c>
       <c r="F5" s="144"/>
       <c r="G5" s="42">
-        <v>44681</v>
+        <v>44651</v>
       </c>
       <c r="H5" s="10"/>
       <c r="I5" s="13"/>

--- a/packages/GB Accounts Self Employed 2022-04-05 (Apr22) Excel 2007/Vat.xlsx
+++ b/packages/GB Accounts Self Employed 2022-04-05 (Apr22) Excel 2007/Vat.xlsx
@@ -23,10 +23,12 @@
     <sheet name="S03Y1" sheetId="26" r:id="rId8"/>
     <sheet name="S04Y2" sheetId="25" r:id="rId9"/>
     <sheet name="S05Y2" sheetId="24" r:id="rId10"/>
+    <sheet name="S06Y2" sheetId="28" r:id="rId22"/>
     <sheet name="P02Y1" sheetId="23" r:id="rId11"/>
     <sheet name="P03Y1" sheetId="22" r:id="rId12"/>
     <sheet name="P04Y2" sheetId="21" r:id="rId13"/>
     <sheet name="P05Y2" sheetId="27" r:id="rId14"/>
+    <sheet name="P06Y2" sheetId="29" r:id="rId23"/>
   </sheets>
   <externalReferences>
     <externalReference r:id="rId15"/>
@@ -1430,6 +1432,11 @@
             <v>44742</v>
           </cell>
         </row>
+        <row r="25">
+          <cell r="B25">
+            <v>44773</v>
+          </cell>
+        </row>
       </sheetData>
     </sheetDataSet>
   </externalBook>
@@ -2398,7 +2405,10 @@
       <c r="G16" s="25"/>
       <c r="H16" s="10"/>
       <c r="I16" s="13"/>
-      <c r="K16" s="69"/>
+      <c r="K16" s="69">
+        <f>[1]Admin!$B$20</f>
+        <v>44742</v>
+      </c>
     </row>
     <row r="17" spans="1:11" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A17" s="68"/>
@@ -2638,7 +2648,7 @@
   <phoneticPr fontId="5" type="noConversion"/>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G5" xr:uid="{00000000-0002-0000-0000-000000000000}">
-      <formula1>$K$2:$K$15</formula1>
+      <formula1>$K$2:$K$16</formula1>
     </dataValidation>
   </dataValidations>
   <printOptions horizontalCentered="1"/>
@@ -11590,6 +11600,4364 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
   <sheetPr codeName="Sheet14"/>
+  <dimension ref="A1:I201"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
+  <cols>
+    <col min="1" max="1" width="8.83203125" style="95" customWidth="1"/>
+    <col min="2" max="2" width="19.6640625" style="89" customWidth="1"/>
+    <col min="3" max="3" width="12.6640625" style="94" customWidth="1"/>
+    <col min="4" max="4" width="5.83203125" style="93" customWidth="1"/>
+    <col min="5" max="5" width="14.6640625" style="92" customWidth="1"/>
+    <col min="6" max="6" width="5.6640625" style="91" customWidth="1"/>
+    <col min="7" max="7" width="10.5" style="90" customWidth="1"/>
+    <col min="8" max="8" width="9.6640625" style="90" customWidth="1"/>
+    <col min="9" max="9" width="10.6640625" style="90" customWidth="1"/>
+    <col min="10" max="16384" width="9.1640625" style="89"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" s="75" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A1" s="151" t="s">
+        <v>39</v>
+      </c>
+      <c r="B1" s="152"/>
+      <c r="C1" s="164" t="s">
+        <v>37</v>
+      </c>
+      <c r="D1" s="169"/>
+      <c r="E1" s="86" t="s">
+        <v>32</v>
+      </c>
+      <c r="F1" s="161"/>
+      <c r="G1" s="86">
+        <f>SUM(G5:G200)</f>
+        <v>0</v>
+      </c>
+      <c r="H1" s="86">
+        <f>SUM(H5:H200)</f>
+        <v>0</v>
+      </c>
+      <c r="I1" s="86">
+        <f>SUM(I5:I200)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" s="105" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A2" s="167" t="s">
+        <v>38</v>
+      </c>
+      <c r="B2" s="157" t="str">
+        <f>IF((I1-SUM(P1:AL1)&lt;&gt;0),"COMPLETE EXPENSE ANALYSIS by inserting expense letter in col F","Supplier")</f>
+        <v>Supplier</v>
+      </c>
+      <c r="C2" s="165"/>
+      <c r="D2" s="162"/>
+      <c r="E2" s="168" t="s">
+        <v>36</v>
+      </c>
+      <c r="F2" s="162"/>
+      <c r="G2" s="157" t="s">
+        <v>35</v>
+      </c>
+      <c r="H2" s="106">
+        <f>[3]ClosingCreditors!$H$2</f>
+        <v>20</v>
+      </c>
+      <c r="I2" s="157" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" s="104" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A3" s="162"/>
+      <c r="B3" s="162"/>
+      <c r="C3" s="165"/>
+      <c r="D3" s="162"/>
+      <c r="E3" s="162"/>
+      <c r="F3" s="162"/>
+      <c r="G3" s="159"/>
+      <c r="H3" s="157" t="s">
+        <v>33</v>
+      </c>
+      <c r="I3" s="159"/>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A4" s="163"/>
+      <c r="B4" s="163"/>
+      <c r="C4" s="166"/>
+      <c r="D4" s="163"/>
+      <c r="E4" s="163"/>
+      <c r="F4" s="163"/>
+      <c r="G4" s="160"/>
+      <c r="H4" s="158"/>
+      <c r="I4" s="160"/>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="B5" s="91"/>
+      <c r="C5" s="93"/>
+      <c r="E5" s="91"/>
+      <c r="F5" s="89"/>
+      <c r="G5" s="103"/>
+      <c r="H5" s="90" t="str">
+        <f t="shared" ref="H5:H14" si="0">IF(G5&lt;&gt;0,G5*H$2/(100+H$2)," ")</f>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I5" s="90" t="str">
+        <f t="shared" ref="I5:I68" si="1">IF((G5&lt;&gt;0),G5-H5," ")</f>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="F6" s="89"/>
+      <c r="H6" s="90" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I6" s="90" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="F7" s="89"/>
+      <c r="H7" s="90" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I7" s="90" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="F8" s="89"/>
+      <c r="H8" s="90" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I8" s="90" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="F9" s="89"/>
+      <c r="H9" s="90" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I9" s="90" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="F10" s="89"/>
+      <c r="H10" s="90" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I10" s="90" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="F11" s="89"/>
+      <c r="H11" s="90" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I11" s="90" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="F12" s="89"/>
+      <c r="H12" s="90" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I12" s="90" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="F13" s="89"/>
+      <c r="H13" s="90" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I13" s="90" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="F14" s="89"/>
+      <c r="H14" s="90" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I14" s="90" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="F15" s="89"/>
+      <c r="H15" s="90" t="str">
+        <f t="shared" ref="H15:H78" si="2">IF(H$4="X"," ",IF(G15&lt;&gt;0,G15*H$2/(100+H$2)," "))</f>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I15" s="90" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="F16" s="89"/>
+      <c r="H16" s="90" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I16" s="90" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="17" spans="5:9" x14ac:dyDescent="0.15">
+      <c r="F17" s="89"/>
+      <c r="H17" s="90" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I17" s="90" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="18" spans="5:9" x14ac:dyDescent="0.15">
+      <c r="F18" s="89"/>
+      <c r="H18" s="90" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I18" s="90" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="19" spans="5:9" x14ac:dyDescent="0.15">
+      <c r="F19" s="89"/>
+      <c r="H19" s="90" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I19" s="90" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="20" spans="5:9" x14ac:dyDescent="0.15">
+      <c r="F20" s="89"/>
+      <c r="H20" s="90" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I20" s="90" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="21" spans="5:9" x14ac:dyDescent="0.15">
+      <c r="F21" s="89"/>
+      <c r="H21" s="90" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I21" s="90" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="22" spans="5:9" x14ac:dyDescent="0.15">
+      <c r="E22" s="89"/>
+      <c r="F22" s="89"/>
+      <c r="H22" s="90" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I22" s="90" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="23" spans="5:9" x14ac:dyDescent="0.15">
+      <c r="E23" s="102"/>
+      <c r="F23" s="89"/>
+      <c r="H23" s="90" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I23" s="90" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="24" spans="5:9" x14ac:dyDescent="0.15">
+      <c r="F24" s="89"/>
+      <c r="H24" s="90" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I24" s="90" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="25" spans="5:9" x14ac:dyDescent="0.15">
+      <c r="F25" s="89"/>
+      <c r="H25" s="90" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I25" s="90" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="26" spans="5:9" x14ac:dyDescent="0.15">
+      <c r="F26" s="89"/>
+      <c r="H26" s="90" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I26" s="90" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="27" spans="5:9" x14ac:dyDescent="0.15">
+      <c r="F27" s="89"/>
+      <c r="H27" s="90" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I27" s="90" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="28" spans="5:9" x14ac:dyDescent="0.15">
+      <c r="F28" s="89"/>
+      <c r="H28" s="90" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I28" s="90" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="29" spans="5:9" x14ac:dyDescent="0.15">
+      <c r="F29" s="89"/>
+      <c r="H29" s="90" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I29" s="90" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="30" spans="5:9" x14ac:dyDescent="0.15">
+      <c r="F30" s="89"/>
+      <c r="H30" s="90" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I30" s="90" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="31" spans="5:9" x14ac:dyDescent="0.15">
+      <c r="F31" s="89"/>
+      <c r="H31" s="90" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I31" s="90" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="32" spans="5:9" x14ac:dyDescent="0.15">
+      <c r="F32" s="89"/>
+      <c r="H32" s="90" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I32" s="90" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="33" spans="6:9" x14ac:dyDescent="0.15">
+      <c r="F33" s="89"/>
+      <c r="H33" s="90" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I33" s="90" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="34" spans="6:9" x14ac:dyDescent="0.15">
+      <c r="F34" s="89"/>
+      <c r="H34" s="90" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I34" s="90" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="35" spans="6:9" x14ac:dyDescent="0.15">
+      <c r="F35" s="89"/>
+      <c r="H35" s="90" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I35" s="90" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="36" spans="6:9" x14ac:dyDescent="0.15">
+      <c r="F36" s="89"/>
+      <c r="H36" s="90" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I36" s="90" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="37" spans="6:9" x14ac:dyDescent="0.15">
+      <c r="F37" s="89"/>
+      <c r="H37" s="90" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I37" s="90" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="38" spans="6:9" x14ac:dyDescent="0.15">
+      <c r="F38" s="89"/>
+      <c r="H38" s="90" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I38" s="90" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="39" spans="6:9" x14ac:dyDescent="0.15">
+      <c r="F39" s="89"/>
+      <c r="H39" s="90" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I39" s="90" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="40" spans="6:9" x14ac:dyDescent="0.15">
+      <c r="F40" s="89"/>
+      <c r="H40" s="90" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I40" s="90" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="41" spans="6:9" x14ac:dyDescent="0.15">
+      <c r="F41" s="89"/>
+      <c r="H41" s="90" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I41" s="90" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="42" spans="6:9" x14ac:dyDescent="0.15">
+      <c r="F42" s="89"/>
+      <c r="H42" s="90" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I42" s="90" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="43" spans="6:9" x14ac:dyDescent="0.15">
+      <c r="F43" s="89"/>
+      <c r="H43" s="90" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I43" s="90" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="44" spans="6:9" x14ac:dyDescent="0.15">
+      <c r="F44" s="89"/>
+      <c r="H44" s="90" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I44" s="90" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="45" spans="6:9" x14ac:dyDescent="0.15">
+      <c r="F45" s="89"/>
+      <c r="H45" s="90" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I45" s="90" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="46" spans="6:9" x14ac:dyDescent="0.15">
+      <c r="F46" s="89"/>
+      <c r="H46" s="90" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I46" s="90" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="47" spans="6:9" x14ac:dyDescent="0.15">
+      <c r="F47" s="89"/>
+      <c r="H47" s="90" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I47" s="90" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="48" spans="6:9" x14ac:dyDescent="0.15">
+      <c r="F48" s="89"/>
+      <c r="H48" s="90" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I48" s="90" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="49" spans="6:9" x14ac:dyDescent="0.15">
+      <c r="F49" s="89"/>
+      <c r="H49" s="90" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I49" s="90" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="50" spans="6:9" x14ac:dyDescent="0.15">
+      <c r="F50" s="89"/>
+      <c r="H50" s="90" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I50" s="90" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="51" spans="6:9" x14ac:dyDescent="0.15">
+      <c r="F51" s="89"/>
+      <c r="H51" s="90" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I51" s="90" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="52" spans="6:9" x14ac:dyDescent="0.15">
+      <c r="F52" s="89"/>
+      <c r="H52" s="90" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I52" s="90" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="53" spans="6:9" x14ac:dyDescent="0.15">
+      <c r="F53" s="89"/>
+      <c r="H53" s="90" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I53" s="90" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="54" spans="6:9" x14ac:dyDescent="0.15">
+      <c r="F54" s="89"/>
+      <c r="H54" s="90" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I54" s="90" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="55" spans="6:9" x14ac:dyDescent="0.15">
+      <c r="F55" s="89"/>
+      <c r="H55" s="90" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I55" s="90" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="56" spans="6:9" x14ac:dyDescent="0.15">
+      <c r="F56" s="89"/>
+      <c r="H56" s="90" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I56" s="90" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="57" spans="6:9" x14ac:dyDescent="0.15">
+      <c r="F57" s="89"/>
+      <c r="H57" s="90" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I57" s="90" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="58" spans="6:9" x14ac:dyDescent="0.15">
+      <c r="F58" s="89"/>
+      <c r="H58" s="90" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I58" s="90" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="59" spans="6:9" x14ac:dyDescent="0.15">
+      <c r="F59" s="89"/>
+      <c r="H59" s="90" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I59" s="90" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="60" spans="6:9" x14ac:dyDescent="0.15">
+      <c r="F60" s="89"/>
+      <c r="H60" s="90" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I60" s="90" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="61" spans="6:9" x14ac:dyDescent="0.15">
+      <c r="F61" s="89"/>
+      <c r="H61" s="90" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I61" s="90" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="62" spans="6:9" x14ac:dyDescent="0.15">
+      <c r="F62" s="89"/>
+      <c r="H62" s="90" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I62" s="90" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="63" spans="6:9" x14ac:dyDescent="0.15">
+      <c r="F63" s="89"/>
+      <c r="H63" s="90" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I63" s="90" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="64" spans="6:9" x14ac:dyDescent="0.15">
+      <c r="F64" s="89"/>
+      <c r="H64" s="90" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I64" s="90" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="65" spans="6:9" x14ac:dyDescent="0.15">
+      <c r="F65" s="89"/>
+      <c r="H65" s="90" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I65" s="90" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="66" spans="6:9" x14ac:dyDescent="0.15">
+      <c r="F66" s="89"/>
+      <c r="H66" s="90" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I66" s="90" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="67" spans="6:9" x14ac:dyDescent="0.15">
+      <c r="F67" s="89"/>
+      <c r="H67" s="90" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I67" s="90" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="68" spans="6:9" x14ac:dyDescent="0.15">
+      <c r="F68" s="89"/>
+      <c r="H68" s="90" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I68" s="90" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="69" spans="6:9" x14ac:dyDescent="0.15">
+      <c r="F69" s="89"/>
+      <c r="H69" s="90" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I69" s="90" t="str">
+        <f t="shared" ref="I69:I132" si="3">IF((G69&lt;&gt;0),G69-H69," ")</f>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="70" spans="6:9" x14ac:dyDescent="0.15">
+      <c r="F70" s="89"/>
+      <c r="H70" s="90" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I70" s="90" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="71" spans="6:9" x14ac:dyDescent="0.15">
+      <c r="F71" s="89"/>
+      <c r="H71" s="90" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I71" s="90" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="72" spans="6:9" x14ac:dyDescent="0.15">
+      <c r="F72" s="89"/>
+      <c r="H72" s="90" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I72" s="90" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="73" spans="6:9" x14ac:dyDescent="0.15">
+      <c r="F73" s="89"/>
+      <c r="H73" s="90" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I73" s="90" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="74" spans="6:9" x14ac:dyDescent="0.15">
+      <c r="F74" s="89"/>
+      <c r="H74" s="90" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I74" s="90" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="75" spans="6:9" x14ac:dyDescent="0.15">
+      <c r="F75" s="89"/>
+      <c r="H75" s="90" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I75" s="90" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="76" spans="6:9" x14ac:dyDescent="0.15">
+      <c r="F76" s="89"/>
+      <c r="H76" s="90" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I76" s="90" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="77" spans="6:9" x14ac:dyDescent="0.15">
+      <c r="F77" s="89"/>
+      <c r="H77" s="90" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I77" s="90" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="78" spans="6:9" x14ac:dyDescent="0.15">
+      <c r="F78" s="89"/>
+      <c r="H78" s="90" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I78" s="90" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="79" spans="6:9" x14ac:dyDescent="0.15">
+      <c r="F79" s="89"/>
+      <c r="H79" s="90" t="str">
+        <f t="shared" ref="H79:H142" si="4">IF(H$4="X"," ",IF(G79&lt;&gt;0,G79*H$2/(100+H$2)," "))</f>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I79" s="90" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="80" spans="6:9" x14ac:dyDescent="0.15">
+      <c r="F80" s="89"/>
+      <c r="H80" s="90" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I80" s="90" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="81" spans="6:9" x14ac:dyDescent="0.15">
+      <c r="F81" s="89"/>
+      <c r="H81" s="90" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I81" s="90" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="82" spans="6:9" x14ac:dyDescent="0.15">
+      <c r="F82" s="89"/>
+      <c r="H82" s="90" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I82" s="90" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="83" spans="6:9" x14ac:dyDescent="0.15">
+      <c r="F83" s="89"/>
+      <c r="H83" s="90" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I83" s="90" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="84" spans="6:9" x14ac:dyDescent="0.15">
+      <c r="F84" s="89"/>
+      <c r="H84" s="90" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I84" s="90" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="85" spans="6:9" x14ac:dyDescent="0.15">
+      <c r="F85" s="89"/>
+      <c r="H85" s="90" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I85" s="90" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="86" spans="6:9" x14ac:dyDescent="0.15">
+      <c r="F86" s="89"/>
+      <c r="H86" s="90" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I86" s="90" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="87" spans="6:9" x14ac:dyDescent="0.15">
+      <c r="F87" s="89"/>
+      <c r="H87" s="90" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I87" s="90" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="88" spans="6:9" x14ac:dyDescent="0.15">
+      <c r="F88" s="89"/>
+      <c r="H88" s="90" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I88" s="90" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="89" spans="6:9" x14ac:dyDescent="0.15">
+      <c r="F89" s="89"/>
+      <c r="H89" s="90" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I89" s="90" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="90" spans="6:9" x14ac:dyDescent="0.15">
+      <c r="F90" s="89"/>
+      <c r="H90" s="90" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I90" s="90" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="91" spans="6:9" x14ac:dyDescent="0.15">
+      <c r="F91" s="89"/>
+      <c r="H91" s="90" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I91" s="90" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="92" spans="6:9" x14ac:dyDescent="0.15">
+      <c r="F92" s="89"/>
+      <c r="H92" s="90" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I92" s="90" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="93" spans="6:9" x14ac:dyDescent="0.15">
+      <c r="F93" s="89"/>
+      <c r="H93" s="90" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I93" s="90" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="94" spans="6:9" x14ac:dyDescent="0.15">
+      <c r="F94" s="89"/>
+      <c r="H94" s="90" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I94" s="90" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="95" spans="6:9" x14ac:dyDescent="0.15">
+      <c r="F95" s="89"/>
+      <c r="H95" s="90" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I95" s="90" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="96" spans="6:9" x14ac:dyDescent="0.15">
+      <c r="F96" s="89"/>
+      <c r="H96" s="90" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I96" s="90" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="97" spans="6:9" x14ac:dyDescent="0.15">
+      <c r="F97" s="89"/>
+      <c r="H97" s="90" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I97" s="90" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="98" spans="6:9" x14ac:dyDescent="0.15">
+      <c r="F98" s="89"/>
+      <c r="H98" s="90" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I98" s="90" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="99" spans="6:9" x14ac:dyDescent="0.15">
+      <c r="F99" s="89"/>
+      <c r="H99" s="90" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I99" s="90" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="100" spans="6:9" x14ac:dyDescent="0.15">
+      <c r="F100" s="89"/>
+      <c r="H100" s="90" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I100" s="90" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="101" spans="6:9" x14ac:dyDescent="0.15">
+      <c r="F101" s="89"/>
+      <c r="H101" s="90" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I101" s="90" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="102" spans="6:9" x14ac:dyDescent="0.15">
+      <c r="F102" s="89"/>
+      <c r="H102" s="90" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I102" s="90" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="103" spans="6:9" x14ac:dyDescent="0.15">
+      <c r="F103" s="89"/>
+      <c r="H103" s="90" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I103" s="90" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="104" spans="6:9" x14ac:dyDescent="0.15">
+      <c r="F104" s="89"/>
+      <c r="H104" s="90" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I104" s="90" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="105" spans="6:9" x14ac:dyDescent="0.15">
+      <c r="F105" s="89"/>
+      <c r="H105" s="90" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I105" s="90" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="106" spans="6:9" x14ac:dyDescent="0.15">
+      <c r="F106" s="89"/>
+      <c r="H106" s="90" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I106" s="90" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="107" spans="6:9" x14ac:dyDescent="0.15">
+      <c r="F107" s="89"/>
+      <c r="H107" s="90" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I107" s="90" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="108" spans="6:9" x14ac:dyDescent="0.15">
+      <c r="F108" s="89"/>
+      <c r="H108" s="90" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I108" s="90" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="109" spans="6:9" x14ac:dyDescent="0.15">
+      <c r="F109" s="89"/>
+      <c r="H109" s="90" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I109" s="90" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="110" spans="6:9" x14ac:dyDescent="0.15">
+      <c r="F110" s="89"/>
+      <c r="H110" s="90" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I110" s="90" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="111" spans="6:9" x14ac:dyDescent="0.15">
+      <c r="F111" s="89"/>
+      <c r="H111" s="90" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I111" s="90" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="112" spans="6:9" x14ac:dyDescent="0.15">
+      <c r="F112" s="89"/>
+      <c r="H112" s="90" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I112" s="90" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="113" spans="6:9" x14ac:dyDescent="0.15">
+      <c r="F113" s="89"/>
+      <c r="H113" s="90" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I113" s="90" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="114" spans="6:9" x14ac:dyDescent="0.15">
+      <c r="F114" s="89"/>
+      <c r="H114" s="90" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I114" s="90" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="115" spans="6:9" x14ac:dyDescent="0.15">
+      <c r="F115" s="89"/>
+      <c r="H115" s="90" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I115" s="90" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="116" spans="6:9" x14ac:dyDescent="0.15">
+      <c r="F116" s="89"/>
+      <c r="H116" s="90" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I116" s="90" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="117" spans="6:9" x14ac:dyDescent="0.15">
+      <c r="F117" s="89"/>
+      <c r="H117" s="90" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I117" s="90" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="118" spans="6:9" x14ac:dyDescent="0.15">
+      <c r="F118" s="89"/>
+      <c r="H118" s="90" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I118" s="90" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="119" spans="6:9" x14ac:dyDescent="0.15">
+      <c r="F119" s="89"/>
+      <c r="H119" s="90" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I119" s="90" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="120" spans="6:9" x14ac:dyDescent="0.15">
+      <c r="F120" s="89"/>
+      <c r="H120" s="90" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I120" s="90" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="121" spans="6:9" x14ac:dyDescent="0.15">
+      <c r="F121" s="89"/>
+      <c r="H121" s="90" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I121" s="90" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="122" spans="6:9" x14ac:dyDescent="0.15">
+      <c r="F122" s="89"/>
+      <c r="H122" s="90" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I122" s="90" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="123" spans="6:9" x14ac:dyDescent="0.15">
+      <c r="F123" s="89"/>
+      <c r="H123" s="90" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I123" s="90" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="124" spans="6:9" x14ac:dyDescent="0.15">
+      <c r="F124" s="89"/>
+      <c r="H124" s="90" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I124" s="90" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="125" spans="6:9" x14ac:dyDescent="0.15">
+      <c r="F125" s="89"/>
+      <c r="H125" s="90" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I125" s="90" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="126" spans="6:9" x14ac:dyDescent="0.15">
+      <c r="F126" s="89"/>
+      <c r="H126" s="90" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I126" s="90" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="127" spans="6:9" x14ac:dyDescent="0.15">
+      <c r="F127" s="89"/>
+      <c r="H127" s="90" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I127" s="90" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="128" spans="6:9" x14ac:dyDescent="0.15">
+      <c r="F128" s="89"/>
+      <c r="H128" s="90" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I128" s="90" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="129" spans="6:9" x14ac:dyDescent="0.15">
+      <c r="F129" s="89"/>
+      <c r="H129" s="90" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I129" s="90" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="130" spans="6:9" x14ac:dyDescent="0.15">
+      <c r="F130" s="89"/>
+      <c r="H130" s="90" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I130" s="90" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="131" spans="6:9" x14ac:dyDescent="0.15">
+      <c r="F131" s="89"/>
+      <c r="H131" s="90" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I131" s="90" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="132" spans="6:9" x14ac:dyDescent="0.15">
+      <c r="F132" s="89"/>
+      <c r="H132" s="90" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I132" s="90" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="133" spans="6:9" x14ac:dyDescent="0.15">
+      <c r="F133" s="89"/>
+      <c r="H133" s="90" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I133" s="90" t="str">
+        <f t="shared" ref="I133:I196" si="5">IF((G133&lt;&gt;0),G133-H133," ")</f>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="134" spans="6:9" x14ac:dyDescent="0.15">
+      <c r="F134" s="89"/>
+      <c r="H134" s="90" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I134" s="90" t="str">
+        <f t="shared" si="5"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="135" spans="6:9" x14ac:dyDescent="0.15">
+      <c r="F135" s="89"/>
+      <c r="H135" s="90" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I135" s="90" t="str">
+        <f t="shared" si="5"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="136" spans="6:9" x14ac:dyDescent="0.15">
+      <c r="F136" s="89"/>
+      <c r="H136" s="90" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I136" s="90" t="str">
+        <f t="shared" si="5"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="137" spans="6:9" x14ac:dyDescent="0.15">
+      <c r="F137" s="89"/>
+      <c r="H137" s="90" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I137" s="90" t="str">
+        <f t="shared" si="5"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="138" spans="6:9" x14ac:dyDescent="0.15">
+      <c r="F138" s="89"/>
+      <c r="H138" s="90" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I138" s="90" t="str">
+        <f t="shared" si="5"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="139" spans="6:9" x14ac:dyDescent="0.15">
+      <c r="F139" s="89"/>
+      <c r="H139" s="90" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I139" s="90" t="str">
+        <f t="shared" si="5"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="140" spans="6:9" x14ac:dyDescent="0.15">
+      <c r="F140" s="89"/>
+      <c r="H140" s="90" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I140" s="90" t="str">
+        <f t="shared" si="5"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="141" spans="6:9" x14ac:dyDescent="0.15">
+      <c r="F141" s="89"/>
+      <c r="H141" s="90" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I141" s="90" t="str">
+        <f t="shared" si="5"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="142" spans="6:9" x14ac:dyDescent="0.15">
+      <c r="F142" s="89"/>
+      <c r="H142" s="90" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I142" s="90" t="str">
+        <f t="shared" si="5"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="143" spans="6:9" x14ac:dyDescent="0.15">
+      <c r="F143" s="89"/>
+      <c r="H143" s="90" t="str">
+        <f t="shared" ref="H143:H200" si="6">IF(H$4="X"," ",IF(G143&lt;&gt;0,G143*H$2/(100+H$2)," "))</f>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I143" s="90" t="str">
+        <f t="shared" si="5"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="144" spans="6:9" x14ac:dyDescent="0.15">
+      <c r="F144" s="89"/>
+      <c r="H144" s="90" t="str">
+        <f t="shared" si="6"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I144" s="90" t="str">
+        <f t="shared" si="5"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="145" spans="6:9" x14ac:dyDescent="0.15">
+      <c r="F145" s="89"/>
+      <c r="H145" s="90" t="str">
+        <f t="shared" si="6"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I145" s="90" t="str">
+        <f t="shared" si="5"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="146" spans="6:9" x14ac:dyDescent="0.15">
+      <c r="F146" s="89"/>
+      <c r="H146" s="90" t="str">
+        <f t="shared" si="6"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I146" s="90" t="str">
+        <f t="shared" si="5"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="147" spans="6:9" x14ac:dyDescent="0.15">
+      <c r="F147" s="89"/>
+      <c r="H147" s="90" t="str">
+        <f t="shared" si="6"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I147" s="90" t="str">
+        <f t="shared" si="5"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="148" spans="6:9" x14ac:dyDescent="0.15">
+      <c r="F148" s="89"/>
+      <c r="H148" s="90" t="str">
+        <f t="shared" si="6"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I148" s="90" t="str">
+        <f t="shared" si="5"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="149" spans="6:9" x14ac:dyDescent="0.15">
+      <c r="F149" s="89"/>
+      <c r="H149" s="90" t="str">
+        <f t="shared" si="6"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I149" s="90" t="str">
+        <f t="shared" si="5"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="150" spans="6:9" x14ac:dyDescent="0.15">
+      <c r="F150" s="89"/>
+      <c r="H150" s="90" t="str">
+        <f t="shared" si="6"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I150" s="90" t="str">
+        <f t="shared" si="5"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="151" spans="6:9" x14ac:dyDescent="0.15">
+      <c r="F151" s="89"/>
+      <c r="H151" s="90" t="str">
+        <f t="shared" si="6"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I151" s="90" t="str">
+        <f t="shared" si="5"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="152" spans="6:9" x14ac:dyDescent="0.15">
+      <c r="F152" s="89"/>
+      <c r="H152" s="90" t="str">
+        <f t="shared" si="6"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I152" s="90" t="str">
+        <f t="shared" si="5"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="153" spans="6:9" x14ac:dyDescent="0.15">
+      <c r="F153" s="89"/>
+      <c r="H153" s="90" t="str">
+        <f t="shared" si="6"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I153" s="90" t="str">
+        <f t="shared" si="5"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="154" spans="6:9" x14ac:dyDescent="0.15">
+      <c r="F154" s="89"/>
+      <c r="H154" s="90" t="str">
+        <f t="shared" si="6"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I154" s="90" t="str">
+        <f t="shared" si="5"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="155" spans="6:9" x14ac:dyDescent="0.15">
+      <c r="F155" s="89"/>
+      <c r="H155" s="90" t="str">
+        <f t="shared" si="6"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I155" s="90" t="str">
+        <f t="shared" si="5"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="156" spans="6:9" x14ac:dyDescent="0.15">
+      <c r="F156" s="89"/>
+      <c r="H156" s="90" t="str">
+        <f t="shared" si="6"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I156" s="90" t="str">
+        <f t="shared" si="5"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="157" spans="6:9" x14ac:dyDescent="0.15">
+      <c r="F157" s="89"/>
+      <c r="H157" s="90" t="str">
+        <f t="shared" si="6"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I157" s="90" t="str">
+        <f t="shared" si="5"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="158" spans="6:9" x14ac:dyDescent="0.15">
+      <c r="F158" s="89"/>
+      <c r="H158" s="90" t="str">
+        <f t="shared" si="6"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I158" s="90" t="str">
+        <f t="shared" si="5"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="159" spans="6:9" x14ac:dyDescent="0.15">
+      <c r="F159" s="89"/>
+      <c r="H159" s="90" t="str">
+        <f t="shared" si="6"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I159" s="90" t="str">
+        <f t="shared" si="5"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="160" spans="6:9" x14ac:dyDescent="0.15">
+      <c r="F160" s="89"/>
+      <c r="H160" s="90" t="str">
+        <f t="shared" si="6"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I160" s="90" t="str">
+        <f t="shared" si="5"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="161" spans="6:9" x14ac:dyDescent="0.15">
+      <c r="F161" s="89"/>
+      <c r="H161" s="90" t="str">
+        <f t="shared" si="6"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I161" s="90" t="str">
+        <f t="shared" si="5"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="162" spans="6:9" x14ac:dyDescent="0.15">
+      <c r="F162" s="89"/>
+      <c r="H162" s="90" t="str">
+        <f t="shared" si="6"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I162" s="90" t="str">
+        <f t="shared" si="5"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="163" spans="6:9" x14ac:dyDescent="0.15">
+      <c r="F163" s="89"/>
+      <c r="H163" s="90" t="str">
+        <f t="shared" si="6"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I163" s="90" t="str">
+        <f t="shared" si="5"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="164" spans="6:9" x14ac:dyDescent="0.15">
+      <c r="F164" s="89"/>
+      <c r="H164" s="90" t="str">
+        <f t="shared" si="6"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I164" s="90" t="str">
+        <f t="shared" si="5"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="165" spans="6:9" x14ac:dyDescent="0.15">
+      <c r="F165" s="89"/>
+      <c r="H165" s="90" t="str">
+        <f t="shared" si="6"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I165" s="90" t="str">
+        <f t="shared" si="5"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="166" spans="6:9" x14ac:dyDescent="0.15">
+      <c r="F166" s="89"/>
+      <c r="H166" s="90" t="str">
+        <f t="shared" si="6"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I166" s="90" t="str">
+        <f t="shared" si="5"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="167" spans="6:9" x14ac:dyDescent="0.15">
+      <c r="F167" s="89"/>
+      <c r="H167" s="90" t="str">
+        <f t="shared" si="6"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I167" s="90" t="str">
+        <f t="shared" si="5"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="168" spans="6:9" x14ac:dyDescent="0.15">
+      <c r="F168" s="89"/>
+      <c r="H168" s="90" t="str">
+        <f t="shared" si="6"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I168" s="90" t="str">
+        <f t="shared" si="5"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="169" spans="6:9" x14ac:dyDescent="0.15">
+      <c r="F169" s="89"/>
+      <c r="H169" s="90" t="str">
+        <f t="shared" si="6"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I169" s="90" t="str">
+        <f t="shared" si="5"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="170" spans="6:9" x14ac:dyDescent="0.15">
+      <c r="F170" s="89"/>
+      <c r="H170" s="90" t="str">
+        <f t="shared" si="6"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I170" s="90" t="str">
+        <f t="shared" si="5"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="171" spans="6:9" x14ac:dyDescent="0.15">
+      <c r="F171" s="89"/>
+      <c r="H171" s="90" t="str">
+        <f t="shared" si="6"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I171" s="90" t="str">
+        <f t="shared" si="5"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="172" spans="6:9" x14ac:dyDescent="0.15">
+      <c r="F172" s="89"/>
+      <c r="H172" s="90" t="str">
+        <f t="shared" si="6"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I172" s="90" t="str">
+        <f t="shared" si="5"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="173" spans="6:9" x14ac:dyDescent="0.15">
+      <c r="F173" s="89"/>
+      <c r="H173" s="90" t="str">
+        <f t="shared" si="6"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I173" s="90" t="str">
+        <f t="shared" si="5"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="174" spans="6:9" x14ac:dyDescent="0.15">
+      <c r="F174" s="89"/>
+      <c r="H174" s="90" t="str">
+        <f t="shared" si="6"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I174" s="90" t="str">
+        <f t="shared" si="5"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="175" spans="6:9" x14ac:dyDescent="0.15">
+      <c r="F175" s="89"/>
+      <c r="H175" s="90" t="str">
+        <f t="shared" si="6"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I175" s="90" t="str">
+        <f t="shared" si="5"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="176" spans="6:9" x14ac:dyDescent="0.15">
+      <c r="F176" s="89"/>
+      <c r="H176" s="90" t="str">
+        <f t="shared" si="6"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I176" s="90" t="str">
+        <f t="shared" si="5"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="177" spans="6:9" x14ac:dyDescent="0.15">
+      <c r="F177" s="89"/>
+      <c r="H177" s="90" t="str">
+        <f t="shared" si="6"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I177" s="90" t="str">
+        <f t="shared" si="5"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="178" spans="6:9" x14ac:dyDescent="0.15">
+      <c r="F178" s="89"/>
+      <c r="H178" s="90" t="str">
+        <f t="shared" si="6"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I178" s="90" t="str">
+        <f t="shared" si="5"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="179" spans="6:9" x14ac:dyDescent="0.15">
+      <c r="F179" s="89"/>
+      <c r="H179" s="90" t="str">
+        <f t="shared" si="6"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I179" s="90" t="str">
+        <f t="shared" si="5"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="180" spans="6:9" x14ac:dyDescent="0.15">
+      <c r="F180" s="89"/>
+      <c r="H180" s="90" t="str">
+        <f t="shared" si="6"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I180" s="90" t="str">
+        <f t="shared" si="5"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="181" spans="6:9" x14ac:dyDescent="0.15">
+      <c r="F181" s="89"/>
+      <c r="H181" s="90" t="str">
+        <f t="shared" si="6"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I181" s="90" t="str">
+        <f t="shared" si="5"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="182" spans="6:9" x14ac:dyDescent="0.15">
+      <c r="F182" s="89"/>
+      <c r="H182" s="90" t="str">
+        <f t="shared" si="6"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I182" s="90" t="str">
+        <f t="shared" si="5"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="183" spans="6:9" x14ac:dyDescent="0.15">
+      <c r="F183" s="89"/>
+      <c r="H183" s="90" t="str">
+        <f t="shared" si="6"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I183" s="90" t="str">
+        <f t="shared" si="5"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="184" spans="6:9" x14ac:dyDescent="0.15">
+      <c r="F184" s="89"/>
+      <c r="H184" s="90" t="str">
+        <f t="shared" si="6"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I184" s="90" t="str">
+        <f t="shared" si="5"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="185" spans="6:9" x14ac:dyDescent="0.15">
+      <c r="F185" s="89"/>
+      <c r="H185" s="90" t="str">
+        <f t="shared" si="6"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I185" s="90" t="str">
+        <f t="shared" si="5"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="186" spans="6:9" x14ac:dyDescent="0.15">
+      <c r="F186" s="89"/>
+      <c r="H186" s="90" t="str">
+        <f t="shared" si="6"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I186" s="90" t="str">
+        <f t="shared" si="5"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="187" spans="6:9" x14ac:dyDescent="0.15">
+      <c r="F187" s="89"/>
+      <c r="H187" s="90" t="str">
+        <f t="shared" si="6"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I187" s="90" t="str">
+        <f t="shared" si="5"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="188" spans="6:9" x14ac:dyDescent="0.15">
+      <c r="F188" s="89"/>
+      <c r="H188" s="90" t="str">
+        <f t="shared" si="6"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I188" s="90" t="str">
+        <f t="shared" si="5"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="189" spans="6:9" x14ac:dyDescent="0.15">
+      <c r="F189" s="89"/>
+      <c r="H189" s="90" t="str">
+        <f t="shared" si="6"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I189" s="90" t="str">
+        <f t="shared" si="5"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="190" spans="6:9" x14ac:dyDescent="0.15">
+      <c r="F190" s="89"/>
+      <c r="H190" s="90" t="str">
+        <f t="shared" si="6"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I190" s="90" t="str">
+        <f t="shared" si="5"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="191" spans="6:9" x14ac:dyDescent="0.15">
+      <c r="F191" s="89"/>
+      <c r="H191" s="90" t="str">
+        <f t="shared" si="6"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I191" s="90" t="str">
+        <f t="shared" si="5"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="192" spans="6:9" x14ac:dyDescent="0.15">
+      <c r="F192" s="89"/>
+      <c r="H192" s="90" t="str">
+        <f t="shared" si="6"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I192" s="90" t="str">
+        <f t="shared" si="5"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="193" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="F193" s="89"/>
+      <c r="H193" s="90" t="str">
+        <f t="shared" si="6"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I193" s="90" t="str">
+        <f t="shared" si="5"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="194" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="F194" s="89"/>
+      <c r="H194" s="90" t="str">
+        <f t="shared" si="6"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I194" s="90" t="str">
+        <f t="shared" si="5"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="195" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="F195" s="89"/>
+      <c r="H195" s="90" t="str">
+        <f t="shared" si="6"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I195" s="90" t="str">
+        <f t="shared" si="5"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="196" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="F196" s="89"/>
+      <c r="H196" s="90" t="str">
+        <f t="shared" si="6"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I196" s="90" t="str">
+        <f t="shared" si="5"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="197" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="F197" s="89"/>
+      <c r="H197" s="90" t="str">
+        <f t="shared" si="6"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I197" s="90" t="str">
+        <f>IF((G197&lt;&gt;0),G197-H197," ")</f>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="198" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="F198" s="89"/>
+      <c r="H198" s="90" t="str">
+        <f t="shared" si="6"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I198" s="90" t="str">
+        <f>IF((G198&lt;&gt;0),G198-H198," ")</f>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="199" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="F199" s="89"/>
+      <c r="H199" s="90" t="str">
+        <f t="shared" si="6"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I199" s="90" t="str">
+        <f>IF((G199&lt;&gt;0),G199-H199," ")</f>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="200" spans="1:9" ht="14" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A200" s="101"/>
+      <c r="B200" s="97"/>
+      <c r="C200" s="100"/>
+      <c r="D200" s="99"/>
+      <c r="E200" s="98"/>
+      <c r="F200" s="97"/>
+      <c r="G200" s="96"/>
+      <c r="H200" s="96" t="str">
+        <f t="shared" si="6"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I200" s="96" t="str">
+        <f>IF((G200&lt;&gt;0),G200-H200," ")</f>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="201" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A201" s="79" t="s">
+        <v>25</v>
+      </c>
+      <c r="H201" s="90" t="str">
+        <f>IF(G201&lt;&gt;0,G201*#REF!/(100+#REF!)," ")</f>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="10">
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="H3:H4"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="C1:C4"/>
+    <mergeCell ref="E2:E4"/>
+    <mergeCell ref="G2:G4"/>
+    <mergeCell ref="A2:A4"/>
+    <mergeCell ref="B2:B4"/>
+    <mergeCell ref="D1:D4"/>
+    <mergeCell ref="F1:F4"/>
+  </mergeCells>
+  <phoneticPr fontId="5" type="noConversion"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter alignWithMargins="0"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0E00-000000000000}">
+  <sheetPr codeName="Sheet15"/>
+  <dimension ref="A1:G201"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
+  <cols>
+    <col min="1" max="1" width="9.1640625" style="79"/>
+    <col min="2" max="2" width="20.1640625" style="76" customWidth="1"/>
+    <col min="3" max="3" width="12.83203125" style="78" customWidth="1"/>
+    <col min="4" max="4" width="7.6640625" style="77" customWidth="1"/>
+    <col min="5" max="5" width="9.6640625" style="76" customWidth="1"/>
+    <col min="6" max="6" width="8.6640625" style="76" customWidth="1"/>
+    <col min="7" max="7" width="9.6640625" style="76" customWidth="1"/>
+    <col min="8" max="16384" width="9.1640625" style="75"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" s="85" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A1" s="151" t="s">
+        <v>39</v>
+      </c>
+      <c r="B1" s="152"/>
+      <c r="C1" s="88" t="s">
+        <v>32</v>
+      </c>
+      <c r="D1" s="87"/>
+      <c r="E1" s="86">
+        <f>SUM(E5:E200)</f>
+        <v>0</v>
+      </c>
+      <c r="F1" s="86">
+        <f>SUM(F5:F200)</f>
+        <v>0</v>
+      </c>
+      <c r="G1" s="86">
+        <f>SUM(G5:G200)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" s="85" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A2" s="153" t="s">
+        <v>31</v>
+      </c>
+      <c r="B2" s="149" t="s">
+        <v>30</v>
+      </c>
+      <c r="C2" s="156" t="s">
+        <v>29</v>
+      </c>
+      <c r="D2" s="147"/>
+      <c r="E2" s="149" t="s">
+        <v>28</v>
+      </c>
+      <c r="F2" s="109">
+        <f>[2]ClosingDebtors!$H$2</f>
+        <v>20</v>
+      </c>
+      <c r="G2" s="149" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" s="84" customFormat="1" ht="26" x14ac:dyDescent="0.15">
+      <c r="A3" s="154"/>
+      <c r="B3" s="155"/>
+      <c r="C3" s="156"/>
+      <c r="D3" s="147"/>
+      <c r="E3" s="149"/>
+      <c r="F3" s="110" t="s">
+        <v>26</v>
+      </c>
+      <c r="G3" s="149"/>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A4" s="150"/>
+      <c r="B4" s="150"/>
+      <c r="C4" s="150"/>
+      <c r="D4" s="148"/>
+      <c r="E4" s="150"/>
+      <c r="F4" s="111">
+        <f>[2]ClosingDebtors!$H$4</f>
+        <v>0</v>
+      </c>
+      <c r="G4" s="150"/>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="F5" s="76" t="str">
+        <f>IF(F$4&gt;0,(IF(E5&lt;&gt;0,E5*F$4/100," ")),IF(E5&lt;&gt;0,E5*F$2/(100+F$2)," "))</f>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="G5" s="76" t="str">
+        <f t="shared" ref="G5:G68" si="0">IF((E5&lt;&gt;0),E5-F5," ")</f>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="F6" s="76" t="str">
+        <f t="shared" ref="F6:F69" si="1">IF(F$4&gt;0,(IF(E6&lt;&gt;0,E6*F$4/100," ")),IF(E6&lt;&gt;0,E6*F$2/(100+F$2)," "))</f>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="G6" s="76" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="F7" s="76" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="G7" s="76" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="F8" s="76" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="G8" s="76" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="F9" s="76" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="G9" s="76" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="F10" s="76" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="G10" s="76" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="F11" s="76" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="G11" s="76" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="F12" s="76" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="G12" s="76" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="F13" s="76" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="G13" s="76" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="F14" s="76" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="G14" s="76" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="F15" s="76" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="G15" s="76" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="F16" s="76" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="G16" s="76" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="17" spans="6:7" x14ac:dyDescent="0.15">
+      <c r="F17" s="76" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="G17" s="76" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="18" spans="6:7" x14ac:dyDescent="0.15">
+      <c r="F18" s="76" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="G18" s="76" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="19" spans="6:7" x14ac:dyDescent="0.15">
+      <c r="F19" s="76" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="G19" s="76" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="20" spans="6:7" x14ac:dyDescent="0.15">
+      <c r="F20" s="76" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="G20" s="76" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="21" spans="6:7" x14ac:dyDescent="0.15">
+      <c r="F21" s="76" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="G21" s="76" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="22" spans="6:7" x14ac:dyDescent="0.15">
+      <c r="F22" s="76" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="G22" s="76" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="23" spans="6:7" x14ac:dyDescent="0.15">
+      <c r="F23" s="76" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="G23" s="76" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="24" spans="6:7" x14ac:dyDescent="0.15">
+      <c r="F24" s="76" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="G24" s="76" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="25" spans="6:7" x14ac:dyDescent="0.15">
+      <c r="F25" s="76" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="G25" s="76" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="26" spans="6:7" x14ac:dyDescent="0.15">
+      <c r="F26" s="76" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="G26" s="76" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="27" spans="6:7" x14ac:dyDescent="0.15">
+      <c r="F27" s="76" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="G27" s="76" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="28" spans="6:7" x14ac:dyDescent="0.15">
+      <c r="F28" s="76" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="G28" s="76" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="29" spans="6:7" x14ac:dyDescent="0.15">
+      <c r="F29" s="76" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="G29" s="76" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="30" spans="6:7" x14ac:dyDescent="0.15">
+      <c r="F30" s="76" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="G30" s="76" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="31" spans="6:7" x14ac:dyDescent="0.15">
+      <c r="F31" s="76" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="G31" s="76" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="32" spans="6:7" x14ac:dyDescent="0.15">
+      <c r="F32" s="76" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="G32" s="76" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="33" spans="6:7" x14ac:dyDescent="0.15">
+      <c r="F33" s="76" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="G33" s="76" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="34" spans="6:7" x14ac:dyDescent="0.15">
+      <c r="F34" s="76" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="G34" s="76" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="35" spans="6:7" x14ac:dyDescent="0.15">
+      <c r="F35" s="76" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="G35" s="76" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="36" spans="6:7" x14ac:dyDescent="0.15">
+      <c r="F36" s="76" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="G36" s="76" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="37" spans="6:7" x14ac:dyDescent="0.15">
+      <c r="F37" s="76" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="G37" s="76" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="38" spans="6:7" x14ac:dyDescent="0.15">
+      <c r="F38" s="76" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="G38" s="76" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="39" spans="6:7" x14ac:dyDescent="0.15">
+      <c r="F39" s="76" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="G39" s="76" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="40" spans="6:7" x14ac:dyDescent="0.15">
+      <c r="F40" s="76" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="G40" s="76" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="41" spans="6:7" x14ac:dyDescent="0.15">
+      <c r="F41" s="76" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="G41" s="76" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="42" spans="6:7" x14ac:dyDescent="0.15">
+      <c r="F42" s="76" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="G42" s="76" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="43" spans="6:7" x14ac:dyDescent="0.15">
+      <c r="F43" s="76" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="G43" s="76" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="44" spans="6:7" x14ac:dyDescent="0.15">
+      <c r="F44" s="76" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="G44" s="76" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="45" spans="6:7" x14ac:dyDescent="0.15">
+      <c r="F45" s="76" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="G45" s="76" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="46" spans="6:7" x14ac:dyDescent="0.15">
+      <c r="F46" s="76" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="G46" s="76" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="47" spans="6:7" x14ac:dyDescent="0.15">
+      <c r="F47" s="76" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="G47" s="76" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="48" spans="6:7" x14ac:dyDescent="0.15">
+      <c r="F48" s="76" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="G48" s="76" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="49" spans="6:7" x14ac:dyDescent="0.15">
+      <c r="F49" s="76" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="G49" s="76" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="50" spans="6:7" x14ac:dyDescent="0.15">
+      <c r="F50" s="76" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="G50" s="76" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="51" spans="6:7" x14ac:dyDescent="0.15">
+      <c r="F51" s="76" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="G51" s="76" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="52" spans="6:7" x14ac:dyDescent="0.15">
+      <c r="F52" s="76" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="G52" s="76" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="53" spans="6:7" x14ac:dyDescent="0.15">
+      <c r="F53" s="76" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="G53" s="76" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="54" spans="6:7" x14ac:dyDescent="0.15">
+      <c r="F54" s="76" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="G54" s="76" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="55" spans="6:7" x14ac:dyDescent="0.15">
+      <c r="F55" s="76" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="G55" s="76" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="56" spans="6:7" x14ac:dyDescent="0.15">
+      <c r="F56" s="76" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="G56" s="76" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="57" spans="6:7" x14ac:dyDescent="0.15">
+      <c r="F57" s="76" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="G57" s="76" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="58" spans="6:7" x14ac:dyDescent="0.15">
+      <c r="F58" s="76" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="G58" s="76" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="59" spans="6:7" x14ac:dyDescent="0.15">
+      <c r="F59" s="76" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="G59" s="76" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="60" spans="6:7" x14ac:dyDescent="0.15">
+      <c r="F60" s="76" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="G60" s="76" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="61" spans="6:7" x14ac:dyDescent="0.15">
+      <c r="F61" s="76" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="G61" s="76" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="62" spans="6:7" x14ac:dyDescent="0.15">
+      <c r="F62" s="76" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="G62" s="76" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="63" spans="6:7" x14ac:dyDescent="0.15">
+      <c r="F63" s="76" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="G63" s="76" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="64" spans="6:7" x14ac:dyDescent="0.15">
+      <c r="F64" s="76" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="G64" s="76" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="65" spans="6:7" x14ac:dyDescent="0.15">
+      <c r="F65" s="76" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="G65" s="76" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="66" spans="6:7" x14ac:dyDescent="0.15">
+      <c r="F66" s="76" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="G66" s="76" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="67" spans="6:7" x14ac:dyDescent="0.15">
+      <c r="F67" s="76" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="G67" s="76" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="68" spans="6:7" x14ac:dyDescent="0.15">
+      <c r="F68" s="76" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="G68" s="76" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="69" spans="6:7" x14ac:dyDescent="0.15">
+      <c r="F69" s="76" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="G69" s="76" t="str">
+        <f t="shared" ref="G69:G132" si="2">IF((E69&lt;&gt;0),E69-F69," ")</f>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="70" spans="6:7" x14ac:dyDescent="0.15">
+      <c r="F70" s="76" t="str">
+        <f t="shared" ref="F70:F133" si="3">IF(F$4&gt;0,(IF(E70&lt;&gt;0,E70*F$4/100," ")),IF(E70&lt;&gt;0,E70*F$2/(100+F$2)," "))</f>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="G70" s="76" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="71" spans="6:7" x14ac:dyDescent="0.15">
+      <c r="F71" s="76" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="G71" s="76" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="72" spans="6:7" x14ac:dyDescent="0.15">
+      <c r="F72" s="76" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="G72" s="76" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="73" spans="6:7" x14ac:dyDescent="0.15">
+      <c r="F73" s="76" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="G73" s="76" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="74" spans="6:7" x14ac:dyDescent="0.15">
+      <c r="F74" s="76" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="G74" s="76" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="75" spans="6:7" x14ac:dyDescent="0.15">
+      <c r="F75" s="76" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="G75" s="76" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="76" spans="6:7" x14ac:dyDescent="0.15">
+      <c r="F76" s="76" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="G76" s="76" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="77" spans="6:7" x14ac:dyDescent="0.15">
+      <c r="F77" s="76" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="G77" s="76" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="78" spans="6:7" x14ac:dyDescent="0.15">
+      <c r="F78" s="76" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="G78" s="76" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="79" spans="6:7" x14ac:dyDescent="0.15">
+      <c r="F79" s="76" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="G79" s="76" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="80" spans="6:7" x14ac:dyDescent="0.15">
+      <c r="F80" s="76" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="G80" s="76" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="81" spans="6:7" x14ac:dyDescent="0.15">
+      <c r="F81" s="76" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="G81" s="76" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="82" spans="6:7" x14ac:dyDescent="0.15">
+      <c r="F82" s="76" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="G82" s="76" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="83" spans="6:7" x14ac:dyDescent="0.15">
+      <c r="F83" s="76" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="G83" s="76" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="84" spans="6:7" x14ac:dyDescent="0.15">
+      <c r="F84" s="76" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="G84" s="76" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="85" spans="6:7" x14ac:dyDescent="0.15">
+      <c r="F85" s="76" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="G85" s="76" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="86" spans="6:7" x14ac:dyDescent="0.15">
+      <c r="F86" s="76" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="G86" s="76" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="87" spans="6:7" x14ac:dyDescent="0.15">
+      <c r="F87" s="76" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="G87" s="76" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="88" spans="6:7" x14ac:dyDescent="0.15">
+      <c r="F88" s="76" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="G88" s="76" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="89" spans="6:7" x14ac:dyDescent="0.15">
+      <c r="F89" s="76" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="G89" s="76" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="90" spans="6:7" x14ac:dyDescent="0.15">
+      <c r="F90" s="76" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="G90" s="76" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="91" spans="6:7" x14ac:dyDescent="0.15">
+      <c r="F91" s="76" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="G91" s="76" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="92" spans="6:7" x14ac:dyDescent="0.15">
+      <c r="F92" s="76" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="G92" s="76" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="93" spans="6:7" x14ac:dyDescent="0.15">
+      <c r="F93" s="76" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="G93" s="76" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="94" spans="6:7" x14ac:dyDescent="0.15">
+      <c r="F94" s="76" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="G94" s="76" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="95" spans="6:7" x14ac:dyDescent="0.15">
+      <c r="F95" s="76" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="G95" s="76" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="96" spans="6:7" x14ac:dyDescent="0.15">
+      <c r="F96" s="76" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="G96" s="76" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="97" spans="6:7" x14ac:dyDescent="0.15">
+      <c r="F97" s="76" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="G97" s="76" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="98" spans="6:7" x14ac:dyDescent="0.15">
+      <c r="F98" s="76" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="G98" s="76" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="99" spans="6:7" x14ac:dyDescent="0.15">
+      <c r="F99" s="76" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="G99" s="76" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="100" spans="6:7" x14ac:dyDescent="0.15">
+      <c r="F100" s="76" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="G100" s="76" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="101" spans="6:7" x14ac:dyDescent="0.15">
+      <c r="F101" s="76" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="G101" s="76" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="102" spans="6:7" x14ac:dyDescent="0.15">
+      <c r="F102" s="76" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="G102" s="76" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="103" spans="6:7" x14ac:dyDescent="0.15">
+      <c r="F103" s="76" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="G103" s="76" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="104" spans="6:7" x14ac:dyDescent="0.15">
+      <c r="F104" s="76" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="G104" s="76" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="105" spans="6:7" x14ac:dyDescent="0.15">
+      <c r="F105" s="76" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="G105" s="76" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="106" spans="6:7" x14ac:dyDescent="0.15">
+      <c r="F106" s="76" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="G106" s="76" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="107" spans="6:7" x14ac:dyDescent="0.15">
+      <c r="F107" s="76" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="G107" s="76" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="108" spans="6:7" x14ac:dyDescent="0.15">
+      <c r="F108" s="76" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="G108" s="76" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="109" spans="6:7" x14ac:dyDescent="0.15">
+      <c r="F109" s="76" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="G109" s="76" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="110" spans="6:7" x14ac:dyDescent="0.15">
+      <c r="F110" s="76" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="G110" s="76" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="111" spans="6:7" x14ac:dyDescent="0.15">
+      <c r="F111" s="76" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="G111" s="76" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="112" spans="6:7" x14ac:dyDescent="0.15">
+      <c r="F112" s="76" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="G112" s="76" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="113" spans="6:7" x14ac:dyDescent="0.15">
+      <c r="F113" s="76" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="G113" s="76" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="114" spans="6:7" x14ac:dyDescent="0.15">
+      <c r="F114" s="76" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="G114" s="76" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="115" spans="6:7" x14ac:dyDescent="0.15">
+      <c r="F115" s="76" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="G115" s="76" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="116" spans="6:7" x14ac:dyDescent="0.15">
+      <c r="F116" s="76" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="G116" s="76" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="117" spans="6:7" x14ac:dyDescent="0.15">
+      <c r="F117" s="76" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="G117" s="76" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="118" spans="6:7" x14ac:dyDescent="0.15">
+      <c r="F118" s="76" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="G118" s="76" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="119" spans="6:7" x14ac:dyDescent="0.15">
+      <c r="F119" s="76" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="G119" s="76" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="120" spans="6:7" x14ac:dyDescent="0.15">
+      <c r="F120" s="76" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="G120" s="76" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="121" spans="6:7" x14ac:dyDescent="0.15">
+      <c r="F121" s="76" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="G121" s="76" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="122" spans="6:7" x14ac:dyDescent="0.15">
+      <c r="F122" s="76" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="G122" s="76" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="123" spans="6:7" x14ac:dyDescent="0.15">
+      <c r="F123" s="76" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="G123" s="76" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="124" spans="6:7" x14ac:dyDescent="0.15">
+      <c r="F124" s="76" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="G124" s="76" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="125" spans="6:7" x14ac:dyDescent="0.15">
+      <c r="F125" s="76" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="G125" s="76" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="126" spans="6:7" x14ac:dyDescent="0.15">
+      <c r="F126" s="76" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="G126" s="76" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="127" spans="6:7" x14ac:dyDescent="0.15">
+      <c r="F127" s="76" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="G127" s="76" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="128" spans="6:7" x14ac:dyDescent="0.15">
+      <c r="F128" s="76" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="G128" s="76" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="129" spans="6:7" x14ac:dyDescent="0.15">
+      <c r="F129" s="76" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="G129" s="76" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="130" spans="6:7" x14ac:dyDescent="0.15">
+      <c r="F130" s="76" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="G130" s="76" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="131" spans="6:7" x14ac:dyDescent="0.15">
+      <c r="F131" s="76" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="G131" s="76" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="132" spans="6:7" x14ac:dyDescent="0.15">
+      <c r="F132" s="76" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="G132" s="76" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="133" spans="6:7" x14ac:dyDescent="0.15">
+      <c r="F133" s="76" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="G133" s="76" t="str">
+        <f t="shared" ref="G133:G195" si="4">IF((E133&lt;&gt;0),E133-F133," ")</f>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="134" spans="6:7" x14ac:dyDescent="0.15">
+      <c r="F134" s="76" t="str">
+        <f t="shared" ref="F134:F197" si="5">IF(F$4&gt;0,(IF(E134&lt;&gt;0,E134*F$4/100," ")),IF(E134&lt;&gt;0,E134*F$2/(100+F$2)," "))</f>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="G134" s="76" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="135" spans="6:7" x14ac:dyDescent="0.15">
+      <c r="F135" s="76" t="str">
+        <f t="shared" si="5"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="G135" s="76" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="136" spans="6:7" x14ac:dyDescent="0.15">
+      <c r="F136" s="76" t="str">
+        <f t="shared" si="5"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="G136" s="76" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="137" spans="6:7" x14ac:dyDescent="0.15">
+      <c r="F137" s="76" t="str">
+        <f t="shared" si="5"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="G137" s="76" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="138" spans="6:7" x14ac:dyDescent="0.15">
+      <c r="F138" s="76" t="str">
+        <f t="shared" si="5"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="G138" s="76" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="139" spans="6:7" x14ac:dyDescent="0.15">
+      <c r="F139" s="76" t="str">
+        <f t="shared" si="5"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="G139" s="76" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="140" spans="6:7" x14ac:dyDescent="0.15">
+      <c r="F140" s="76" t="str">
+        <f t="shared" si="5"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="G140" s="76" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="141" spans="6:7" x14ac:dyDescent="0.15">
+      <c r="F141" s="76" t="str">
+        <f t="shared" si="5"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="G141" s="76" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="142" spans="6:7" x14ac:dyDescent="0.15">
+      <c r="F142" s="76" t="str">
+        <f t="shared" si="5"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="G142" s="76" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="143" spans="6:7" x14ac:dyDescent="0.15">
+      <c r="F143" s="76" t="str">
+        <f t="shared" si="5"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="G143" s="76" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="144" spans="6:7" x14ac:dyDescent="0.15">
+      <c r="F144" s="76" t="str">
+        <f t="shared" si="5"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="G144" s="76" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="145" spans="6:7" x14ac:dyDescent="0.15">
+      <c r="F145" s="76" t="str">
+        <f t="shared" si="5"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="G145" s="76" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="146" spans="6:7" x14ac:dyDescent="0.15">
+      <c r="F146" s="76" t="str">
+        <f t="shared" si="5"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="G146" s="76" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="147" spans="6:7" x14ac:dyDescent="0.15">
+      <c r="F147" s="76" t="str">
+        <f t="shared" si="5"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="G147" s="76" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="148" spans="6:7" x14ac:dyDescent="0.15">
+      <c r="F148" s="76" t="str">
+        <f t="shared" si="5"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="G148" s="76" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="149" spans="6:7" x14ac:dyDescent="0.15">
+      <c r="F149" s="76" t="str">
+        <f t="shared" si="5"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="G149" s="76" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="150" spans="6:7" x14ac:dyDescent="0.15">
+      <c r="F150" s="76" t="str">
+        <f t="shared" si="5"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="G150" s="76" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="151" spans="6:7" x14ac:dyDescent="0.15">
+      <c r="F151" s="76" t="str">
+        <f t="shared" si="5"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="G151" s="76" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="152" spans="6:7" x14ac:dyDescent="0.15">
+      <c r="F152" s="76" t="str">
+        <f t="shared" si="5"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="G152" s="76" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="153" spans="6:7" x14ac:dyDescent="0.15">
+      <c r="F153" s="76" t="str">
+        <f t="shared" si="5"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="G153" s="76" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="154" spans="6:7" x14ac:dyDescent="0.15">
+      <c r="F154" s="76" t="str">
+        <f t="shared" si="5"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="G154" s="76" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="155" spans="6:7" x14ac:dyDescent="0.15">
+      <c r="F155" s="76" t="str">
+        <f t="shared" si="5"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="G155" s="76" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="156" spans="6:7" x14ac:dyDescent="0.15">
+      <c r="F156" s="76" t="str">
+        <f t="shared" si="5"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="G156" s="76" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="157" spans="6:7" x14ac:dyDescent="0.15">
+      <c r="F157" s="76" t="str">
+        <f t="shared" si="5"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="G157" s="76" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="158" spans="6:7" x14ac:dyDescent="0.15">
+      <c r="F158" s="76" t="str">
+        <f t="shared" si="5"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="G158" s="76" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="159" spans="6:7" x14ac:dyDescent="0.15">
+      <c r="F159" s="76" t="str">
+        <f t="shared" si="5"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="G159" s="76" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="160" spans="6:7" x14ac:dyDescent="0.15">
+      <c r="F160" s="76" t="str">
+        <f t="shared" si="5"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="G160" s="76" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="161" spans="6:7" x14ac:dyDescent="0.15">
+      <c r="F161" s="76" t="str">
+        <f t="shared" si="5"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="G161" s="76" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="162" spans="6:7" x14ac:dyDescent="0.15">
+      <c r="F162" s="76" t="str">
+        <f t="shared" si="5"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="G162" s="76" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="163" spans="6:7" x14ac:dyDescent="0.15">
+      <c r="F163" s="76" t="str">
+        <f t="shared" si="5"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="G163" s="76" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="164" spans="6:7" x14ac:dyDescent="0.15">
+      <c r="F164" s="76" t="str">
+        <f t="shared" si="5"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="G164" s="76" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="165" spans="6:7" x14ac:dyDescent="0.15">
+      <c r="F165" s="76" t="str">
+        <f t="shared" si="5"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="G165" s="76" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="166" spans="6:7" x14ac:dyDescent="0.15">
+      <c r="F166" s="76" t="str">
+        <f t="shared" si="5"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="G166" s="76" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="167" spans="6:7" x14ac:dyDescent="0.15">
+      <c r="F167" s="76" t="str">
+        <f t="shared" si="5"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="G167" s="76" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="168" spans="6:7" x14ac:dyDescent="0.15">
+      <c r="F168" s="76" t="str">
+        <f t="shared" si="5"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="G168" s="76" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="169" spans="6:7" x14ac:dyDescent="0.15">
+      <c r="F169" s="76" t="str">
+        <f t="shared" si="5"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="G169" s="76" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="170" spans="6:7" x14ac:dyDescent="0.15">
+      <c r="F170" s="76" t="str">
+        <f t="shared" si="5"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="G170" s="76" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="171" spans="6:7" x14ac:dyDescent="0.15">
+      <c r="F171" s="76" t="str">
+        <f t="shared" si="5"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="G171" s="76" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="172" spans="6:7" x14ac:dyDescent="0.15">
+      <c r="F172" s="76" t="str">
+        <f t="shared" si="5"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="G172" s="76" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="173" spans="6:7" x14ac:dyDescent="0.15">
+      <c r="F173" s="76" t="str">
+        <f t="shared" si="5"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="G173" s="76" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="174" spans="6:7" x14ac:dyDescent="0.15">
+      <c r="F174" s="76" t="str">
+        <f t="shared" si="5"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="G174" s="76" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="175" spans="6:7" x14ac:dyDescent="0.15">
+      <c r="F175" s="76" t="str">
+        <f t="shared" si="5"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="G175" s="76" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="176" spans="6:7" x14ac:dyDescent="0.15">
+      <c r="F176" s="76" t="str">
+        <f t="shared" si="5"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="G176" s="76" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="177" spans="6:7" x14ac:dyDescent="0.15">
+      <c r="F177" s="76" t="str">
+        <f t="shared" si="5"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="G177" s="76" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="178" spans="6:7" x14ac:dyDescent="0.15">
+      <c r="F178" s="76" t="str">
+        <f t="shared" si="5"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="G178" s="76" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="179" spans="6:7" x14ac:dyDescent="0.15">
+      <c r="F179" s="76" t="str">
+        <f t="shared" si="5"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="G179" s="76" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="180" spans="6:7" x14ac:dyDescent="0.15">
+      <c r="F180" s="76" t="str">
+        <f t="shared" si="5"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="G180" s="76" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="181" spans="6:7" x14ac:dyDescent="0.15">
+      <c r="F181" s="76" t="str">
+        <f t="shared" si="5"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="G181" s="76" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="182" spans="6:7" x14ac:dyDescent="0.15">
+      <c r="F182" s="76" t="str">
+        <f t="shared" si="5"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="G182" s="76" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="183" spans="6:7" x14ac:dyDescent="0.15">
+      <c r="F183" s="76" t="str">
+        <f t="shared" si="5"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="G183" s="76" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="184" spans="6:7" x14ac:dyDescent="0.15">
+      <c r="F184" s="76" t="str">
+        <f t="shared" si="5"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="G184" s="76" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="185" spans="6:7" x14ac:dyDescent="0.15">
+      <c r="F185" s="76" t="str">
+        <f t="shared" si="5"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="G185" s="76" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="186" spans="6:7" x14ac:dyDescent="0.15">
+      <c r="F186" s="76" t="str">
+        <f t="shared" si="5"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="G186" s="76" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="187" spans="6:7" x14ac:dyDescent="0.15">
+      <c r="F187" s="76" t="str">
+        <f t="shared" si="5"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="G187" s="76" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="188" spans="6:7" x14ac:dyDescent="0.15">
+      <c r="F188" s="76" t="str">
+        <f t="shared" si="5"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="G188" s="76" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="189" spans="6:7" x14ac:dyDescent="0.15">
+      <c r="F189" s="76" t="str">
+        <f t="shared" si="5"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="G189" s="76" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="190" spans="6:7" x14ac:dyDescent="0.15">
+      <c r="F190" s="76" t="str">
+        <f t="shared" si="5"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="G190" s="76" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="191" spans="6:7" x14ac:dyDescent="0.15">
+      <c r="F191" s="76" t="str">
+        <f t="shared" si="5"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="G191" s="76" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="192" spans="6:7" x14ac:dyDescent="0.15">
+      <c r="F192" s="76" t="str">
+        <f t="shared" si="5"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="G192" s="76" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="193" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="F193" s="76" t="str">
+        <f t="shared" si="5"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="G193" s="76" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="194" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="F194" s="76" t="str">
+        <f t="shared" si="5"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="G194" s="76" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="195" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="F195" s="76" t="str">
+        <f t="shared" si="5"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="G195" s="76" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="196" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="F196" s="76" t="str">
+        <f t="shared" si="5"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="G196" s="76" t="str">
+        <f>IF((E196&lt;&gt;0),E196-F196," ")</f>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="197" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="F197" s="76" t="str">
+        <f t="shared" si="5"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="G197" s="76" t="str">
+        <f>IF((E197&lt;&gt;0),E197-F197," ")</f>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="198" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="F198" s="76" t="str">
+        <f>IF(F$4&gt;0,(IF(E198&lt;&gt;0,E198*F$4/100," ")),IF(E198&lt;&gt;0,E198*F$2/(100+F$2)," "))</f>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="G198" s="76" t="str">
+        <f>IF((E198&lt;&gt;0),E198-F198," ")</f>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="199" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="F199" s="76" t="str">
+        <f>IF(F$4&gt;0,(IF(E199&lt;&gt;0,E199*F$4/100," ")),IF(E199&lt;&gt;0,E199*F$2/(100+F$2)," "))</f>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="G199" s="76" t="str">
+        <f>IF((E199&lt;&gt;0),E199-F199," ")</f>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="200" spans="1:7" ht="14" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A200" s="83"/>
+      <c r="B200" s="80"/>
+      <c r="C200" s="82"/>
+      <c r="D200" s="81"/>
+      <c r="E200" s="80"/>
+      <c r="F200" s="80" t="str">
+        <f>IF(F$4&gt;0,(IF(E200&lt;&gt;0,E200*F$4/100," ")),IF(E200&lt;&gt;0,E200*F$2/(100+F$2)," "))</f>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="G200" s="80" t="str">
+        <f>IF((E200&lt;&gt;0),E200-F200," ")</f>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="201" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A201" s="79" t="s">
+        <v>25</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="7">
+    <mergeCell ref="D2:D4"/>
+    <mergeCell ref="E2:E4"/>
+    <mergeCell ref="G2:G4"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A2:A4"/>
+    <mergeCell ref="B2:B4"/>
+    <mergeCell ref="C2:C4"/>
+  </mergeCells>
+  <phoneticPr fontId="5" type="noConversion"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter alignWithMargins="0"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0F00-000000000000}">
+  <sheetPr codeName="Sheet16"/>
   <dimension ref="A1:I201"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
   <cols>
@@ -14169,7 +18537,10 @@
       <c r="G16" s="25"/>
       <c r="H16" s="10"/>
       <c r="I16" s="13"/>
-      <c r="K16" s="69"/>
+      <c r="K16" s="69">
+        <f>[1]Admin!$B$20</f>
+        <v>44742</v>
+      </c>
     </row>
     <row r="17" spans="1:11" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A17" s="68"/>
@@ -14409,7 +18780,7 @@
   <phoneticPr fontId="5" type="noConversion"/>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G5" xr:uid="{00000000-0002-0000-0100-000000000000}">
-      <formula1>$K$2:$K$15</formula1>
+      <formula1>$K$2:$K$16</formula1>
     </dataValidation>
   </dataValidations>
   <printOptions horizontalCentered="1"/>
@@ -14715,7 +19086,10 @@
       <c r="G16" s="25"/>
       <c r="H16" s="10"/>
       <c r="I16" s="13"/>
-      <c r="K16" s="69"/>
+      <c r="K16" s="69">
+        <f>[1]Admin!$B$20</f>
+        <v>44742</v>
+      </c>
     </row>
     <row r="17" spans="1:11" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A17" s="68"/>
@@ -14955,7 +19329,7 @@
   <phoneticPr fontId="5" type="noConversion"/>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G5" xr:uid="{00000000-0002-0000-0200-000000000000}">
-      <formula1>$K$2:$K$15</formula1>
+      <formula1>$K$2:$K$16</formula1>
     </dataValidation>
   </dataValidations>
   <printOptions horizontalCentered="1"/>
@@ -15261,7 +19635,10 @@
       <c r="G16" s="25"/>
       <c r="H16" s="10"/>
       <c r="I16" s="13"/>
-      <c r="K16" s="69"/>
+      <c r="K16" s="69">
+        <f>[1]Admin!$B$20</f>
+        <v>44742</v>
+      </c>
     </row>
     <row r="17" spans="1:11" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A17" s="68"/>
@@ -15501,7 +19878,7 @@
   <phoneticPr fontId="5" type="noConversion"/>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G5" xr:uid="{00000000-0002-0000-0300-000000000000}">
-      <formula1>$K$2:$K$15</formula1>
+      <formula1>$K$2:$K$16</formula1>
     </dataValidation>
   </dataValidations>
   <printOptions horizontalCentered="1"/>
@@ -15606,7 +19983,7 @@
       </c>
       <c r="F5" s="144"/>
       <c r="G5" s="42">
-        <v>44712</v>
+        <v>44742</v>
       </c>
       <c r="H5" s="10"/>
       <c r="I5" s="13"/>
@@ -15807,7 +20184,10 @@
       <c r="G16" s="25"/>
       <c r="H16" s="10"/>
       <c r="I16" s="13"/>
-      <c r="K16" s="69"/>
+      <c r="K16" s="69">
+        <f>[1]Admin!$B$20</f>
+        <v>44742</v>
+      </c>
     </row>
     <row r="17" spans="1:11" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A17" s="68"/>
@@ -16047,7 +20427,7 @@
   <phoneticPr fontId="5" type="noConversion"/>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G5" xr:uid="{00000000-0002-0000-0400-000000000000}">
-      <formula1>$K$2:$K$15</formula1>
+      <formula1>$K$2:$K$16</formula1>
     </dataValidation>
   </dataValidations>
   <printOptions horizontalCentered="1"/>
@@ -16063,7 +20443,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <sheetPr codeName="Sheet6"/>
-  <dimension ref="A1:N20"/>
+  <dimension ref="A1:N21"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="2" style="44" customWidth="1"/>
@@ -16862,7 +21242,7 @@
         <f>[1]Admin!$B$19</f>
         <v>44712</v>
       </c>
-      <c r="C19" s="63">
+      <c r="C19" s="62">
         <f>[1]Admin!$B$20</f>
         <v>44742</v>
       </c>
@@ -16905,21 +21285,70 @@
       </c>
       <c r="N19" s="57"/>
     </row>
-    <row r="20" spans="1:14" ht="9" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="58"/>
-      <c r="B20" s="59"/>
-      <c r="C20" s="59"/>
-      <c r="D20" s="60"/>
-      <c r="E20" s="60"/>
-      <c r="F20" s="60"/>
-      <c r="G20" s="60"/>
-      <c r="H20" s="60"/>
-      <c r="I20" s="60"/>
-      <c r="J20" s="60"/>
-      <c r="K20" s="60"/>
-      <c r="L20" s="123"/>
-      <c r="M20" s="124"/>
-      <c r="N20" s="61"/>
+    <row r="20" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="A20" s="56"/>
+      <c r="B20" s="62">
+        <f>[1]Admin!$B$20</f>
+        <v>44742</v>
+      </c>
+      <c r="C20" s="63">
+        <f>[1]Admin!$B$25</f>
+        <v>44773</v>
+      </c>
+      <c r="D20" s="107">
+        <f>S06Y2!$G$1</f>
+        <v>0</v>
+      </c>
+      <c r="E20" s="108">
+        <f>SUM(D18:D20)</f>
+        <v>0</v>
+      </c>
+      <c r="F20" s="108">
+        <f>S06Y2!$F$1</f>
+        <v>0</v>
+      </c>
+      <c r="G20" s="108">
+        <f>SUM(F18:F20)</f>
+        <v>0</v>
+      </c>
+      <c r="H20" s="108">
+        <f>P06Y2!$I$1</f>
+        <v>0</v>
+      </c>
+      <c r="I20" s="108">
+        <f>SUM(H18:H20)</f>
+        <v>0</v>
+      </c>
+      <c r="J20" s="108">
+        <f>P06Y2!$H$1</f>
+        <v>0</v>
+      </c>
+      <c r="K20" s="108">
+        <f>SUM(J18:J20)</f>
+        <v>0</v>
+      </c>
+      <c r="L20" s="121"/>
+      <c r="M20" s="122">
+        <f>IF([2]Mar!$H$4&gt;0,[2]Mar!$H$4,0)</f>
+        <v>0</v>
+      </c>
+      <c r="N20" s="57"/>
+    </row>
+    <row r="21" spans="1:14" ht="9" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A21" s="58"/>
+      <c r="B21" s="59"/>
+      <c r="C21" s="59"/>
+      <c r="D21" s="60"/>
+      <c r="E21" s="60"/>
+      <c r="F21" s="60"/>
+      <c r="G21" s="60"/>
+      <c r="H21" s="60"/>
+      <c r="I21" s="60"/>
+      <c r="J21" s="60"/>
+      <c r="K21" s="60"/>
+      <c r="L21" s="123"/>
+      <c r="M21" s="124"/>
+      <c r="N21" s="61"/>
     </row>
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>

--- a/packages/GB Accounts Self Employed 2022-04-05 (Apr22) Excel 2007/Vat.xlsx
+++ b/packages/GB Accounts Self Employed 2022-04-05 (Apr22) Excel 2007/Vat.xlsx
@@ -2239,7 +2239,7 @@
       <c r="F7" s="146"/>
       <c r="G7" s="19">
         <f>LOOKUP(G$5,Vatinterface!B:B,Vatinterface!C:C)</f>
-        <v>45869</v>
+        <v>44408</v>
       </c>
       <c r="H7" s="10"/>
       <c r="I7" s="13"/>
@@ -18371,7 +18371,7 @@
       <c r="F7" s="146"/>
       <c r="G7" s="19">
         <f>LOOKUP(G$5,Vatinterface!B:B,Vatinterface!C:C)</f>
-        <v>45961</v>
+        <v>44500</v>
       </c>
       <c r="H7" s="10"/>
       <c r="I7" s="13"/>
@@ -18920,7 +18920,7 @@
       <c r="F7" s="146"/>
       <c r="G7" s="19">
         <f>LOOKUP(G$5,Vatinterface!B:B,Vatinterface!C:C)</f>
-        <v>46053</v>
+        <v>44592</v>
       </c>
       <c r="H7" s="10"/>
       <c r="I7" s="13"/>
@@ -19469,7 +19469,7 @@
       <c r="F7" s="146"/>
       <c r="G7" s="19">
         <f>LOOKUP(G$5,Vatinterface!B:B,Vatinterface!C:C)</f>
-        <v>46142</v>
+        <v>44681</v>
       </c>
       <c r="H7" s="10"/>
       <c r="I7" s="13"/>
@@ -20018,7 +20018,7 @@
       <c r="F7" s="146"/>
       <c r="G7" s="19">
         <f>LOOKUP(G$5,Vatinterface!B:B,Vatinterface!C:C)</f>
-        <v>46173</v>
+        <v>44773</v>
       </c>
       <c r="H7" s="10"/>
       <c r="I7" s="13"/>
@@ -20533,7 +20533,7 @@
       </c>
       <c r="C4" s="62">
         <f>B5</f>
-        <v>45747</v>
+        <v>44286</v>
       </c>
       <c r="D4" s="107">
         <f>S02Y1!$G$1</f>
@@ -20570,7 +20570,7 @@
       </c>
       <c r="C5" s="62">
         <f t="shared" ref="C5:C18" si="0">B6</f>
-        <v>45777</v>
+        <v>44316</v>
       </c>
       <c r="D5" s="107">
         <f>S03Y1!$G$1</f>
@@ -20607,7 +20607,7 @@
       </c>
       <c r="C6" s="62">
         <f t="shared" si="0"/>
-        <v>45808</v>
+        <v>44347</v>
       </c>
       <c r="D6" s="107">
         <f>[2]Apr!$I$1</f>
@@ -20656,7 +20656,7 @@
       </c>
       <c r="C7" s="62">
         <f t="shared" si="0"/>
-        <v>45838</v>
+        <v>44377</v>
       </c>
       <c r="D7" s="107">
         <f>[2]May!$I$1</f>
@@ -20705,7 +20705,7 @@
       </c>
       <c r="C8" s="62">
         <f t="shared" si="0"/>
-        <v>45869</v>
+        <v>44408</v>
       </c>
       <c r="D8" s="107">
         <f>[2]Jun!$I$1</f>
@@ -20754,7 +20754,7 @@
       </c>
       <c r="C9" s="62">
         <f t="shared" si="0"/>
-        <v>45900</v>
+        <v>44439</v>
       </c>
       <c r="D9" s="107">
         <f>[2]Jul!$I$1</f>
@@ -20803,7 +20803,7 @@
       </c>
       <c r="C10" s="62">
         <f t="shared" si="0"/>
-        <v>45930</v>
+        <v>44469</v>
       </c>
       <c r="D10" s="107">
         <f>[2]Aug!$I$1</f>
@@ -20852,7 +20852,7 @@
       </c>
       <c r="C11" s="62">
         <f t="shared" si="0"/>
-        <v>45961</v>
+        <v>44500</v>
       </c>
       <c r="D11" s="107">
         <f>[2]Sep!$I$1</f>
@@ -20901,7 +20901,7 @@
       </c>
       <c r="C12" s="62">
         <f t="shared" si="0"/>
-        <v>45991</v>
+        <v>44530</v>
       </c>
       <c r="D12" s="107">
         <f>[2]Oct!$I$1</f>
@@ -20950,7 +20950,7 @@
       </c>
       <c r="C13" s="62">
         <f t="shared" si="0"/>
-        <v>46022</v>
+        <v>44561</v>
       </c>
       <c r="D13" s="107">
         <f>[2]Nov!$I$1</f>
@@ -20999,7 +20999,7 @@
       </c>
       <c r="C14" s="62">
         <f t="shared" si="0"/>
-        <v>46053</v>
+        <v>44592</v>
       </c>
       <c r="D14" s="107">
         <f>[2]Dec!$I$1</f>
@@ -21048,7 +21048,7 @@
       </c>
       <c r="C15" s="62">
         <f t="shared" si="0"/>
-        <v>46081</v>
+        <v>44620</v>
       </c>
       <c r="D15" s="107">
         <f>[2]Jan!$I$1</f>
@@ -21097,7 +21097,7 @@
       </c>
       <c r="C16" s="62">
         <f t="shared" si="0"/>
-        <v>46112</v>
+        <v>44651</v>
       </c>
       <c r="D16" s="107">
         <f>[2]Feb!$I$1</f>
@@ -21146,7 +21146,7 @@
       </c>
       <c r="C17" s="62">
         <f t="shared" si="0"/>
-        <v>46142</v>
+        <v>44681</v>
       </c>
       <c r="D17" s="107">
         <f>[2]Mar!$I$1</f>
@@ -21195,7 +21195,7 @@
       </c>
       <c r="C18" s="62">
         <f t="shared" si="0"/>
-        <v>46173</v>
+        <v>44712</v>
       </c>
       <c r="D18" s="107">
         <f>S04Y2!$G$1</f>

--- a/packages/GB Accounts Self Employed 2022-04-05 (Apr22) Excel 2007/Vat.xlsx
+++ b/packages/GB Accounts Self Employed 2022-04-05 (Apr22) Excel 2007/Vat.xlsx
@@ -6995,10 +6995,7 @@
       <c r="A201" s="79" t="s">
         <v>25</v>
       </c>
-      <c r="H201" s="90" t="str">
-        <f>IF(G201&lt;&gt;0,G201*#REF!/(100+#REF!)," ")</f>
-        <v xml:space="preserve"> </v>
-      </c>
+      <c r="H201" s="90"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -9284,10 +9281,7 @@
       <c r="A201" s="79" t="s">
         <v>25</v>
       </c>
-      <c r="H201" s="90" t="str">
-        <f>IF(G201&lt;&gt;0,G201*#REF!/(100+#REF!)," ")</f>
-        <v xml:space="preserve"> </v>
-      </c>
+      <c r="H201" s="90"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -11573,10 +11567,7 @@
       <c r="A201" s="79" t="s">
         <v>25</v>
       </c>
-      <c r="H201" s="90" t="str">
-        <f>IF(G201&lt;&gt;0,G201*#REF!/(100+#REF!)," ")</f>
-        <v xml:space="preserve"> </v>
-      </c>
+      <c r="H201" s="90"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -13862,10 +13853,7 @@
       <c r="A201" s="79" t="s">
         <v>25</v>
       </c>
-      <c r="H201" s="90" t="str">
-        <f>IF(G201&lt;&gt;0,G201*#REF!/(100+#REF!)," ")</f>
-        <v xml:space="preserve"> </v>
-      </c>
+      <c r="H201" s="90"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -18220,10 +18208,7 @@
       <c r="A201" s="79" t="s">
         <v>25</v>
       </c>
-      <c r="H201" s="90" t="str">
-        <f>IF(G201&lt;&gt;0,G201*#REF!/(100+#REF!)," ")</f>
-        <v xml:space="preserve"> </v>
-      </c>
+      <c r="H201" s="90"/>
     </row>
   </sheetData>
   <mergeCells count="10">
